--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C18.1n7/RANDOMSEARCH_DETAILS_C18.1n7.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C18.1n7/RANDOMSEARCH_DETAILS_C18.1n7.xlsx
@@ -469,17 +469,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9731</v>
+        <v>0.9347</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2706</v>
+        <v>0.3655</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.6421</v>
       </c>
     </row>
     <row r="3">
@@ -498,17 +498,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>0.9686</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3064</v>
+        <v>0.3067</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.6451</v>
       </c>
     </row>
     <row r="4">
@@ -527,17 +527,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9495</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2601</v>
+        <v>0.3401</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.6069</v>
       </c>
     </row>
     <row r="5">
@@ -556,17 +556,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8996</v>
+        <v>0.8998</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3773</v>
+        <v>0.3772</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.6921</v>
       </c>
     </row>
     <row r="6">
@@ -585,17 +585,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8187</v>
+        <v>0.8186</v>
       </c>
       <c r="F6" t="n">
         <v>0.4415</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.6885</v>
       </c>
     </row>
     <row r="7">
@@ -614,17 +614,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9185</v>
+        <v>0.919</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3528</v>
+        <v>0.3531</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.6755</v>
       </c>
     </row>
     <row r="8">
@@ -643,17 +643,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9351</v>
+        <v>0.9349</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3489</v>
+        <v>0.3493</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.6612</v>
       </c>
     </row>
     <row r="9">
@@ -672,17 +672,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9535</v>
+        <v>0.974</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3403</v>
+        <v>0.2779</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.6369</v>
       </c>
     </row>
     <row r="10">
@@ -701,17 +701,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9391</v>
+        <v>0.9392</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3337</v>
+        <v>0.3332</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.6612</v>
       </c>
     </row>
     <row r="11">
@@ -730,17 +730,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9283</v>
+        <v>0.9277</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3518</v>
+        <v>0.3526</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.6645</v>
       </c>
     </row>
     <row r="12">
@@ -759,17 +759,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9267</v>
+        <v>0.9257</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3531</v>
+        <v>0.3544</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.6683</v>
       </c>
     </row>
     <row r="13">
@@ -788,17 +788,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9237</v>
+        <v>0.9537</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3531</v>
+        <v>0.3039</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.6641</v>
       </c>
     </row>
     <row r="14">
@@ -817,17 +817,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>0.9286</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3495</v>
+        <v>0.3494</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.6637999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -846,17 +846,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9546</v>
+        <v>0.9553</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3038</v>
+        <v>0.3035</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.666</v>
       </c>
     </row>
     <row r="16">
@@ -875,17 +875,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9281</v>
+        <v>0.953</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3515</v>
+        <v>0.3049</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.6653</v>
       </c>
     </row>
     <row r="17">
@@ -904,17 +904,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9232</v>
+        <v>0.9235</v>
       </c>
       <c r="F17" t="n">
         <v>0.3532</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.6657999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -933,17 +933,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9625</v>
+        <v>0.9623</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3174</v>
+        <v>0.3175</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.6435999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -962,17 +962,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9513</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3261</v>
+        <v>0.326</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.6473</v>
       </c>
     </row>
     <row r="20">
@@ -991,17 +991,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9038</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4168</v>
+        <v>0.4167</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.6647999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9388</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3443</v>
+        <v>0.3311</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.6624</v>
       </c>
     </row>
     <row r="22">
@@ -1049,17 +1049,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9462</v>
+        <v>0.9454</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3299</v>
+        <v>0.3311</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.6616</v>
       </c>
     </row>
     <row r="23">
@@ -1078,17 +1078,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9459</v>
+        <v>0.9452</v>
       </c>
       <c r="F23" t="n">
-        <v>0.337</v>
+        <v>0.3378</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.6622</v>
       </c>
     </row>
     <row r="24">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E24" t="n">
         <v>0.8882</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4241</v>
+        <v>0.424</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.6652</v>
       </c>
     </row>
     <row r="25">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1146,7 +1146,7 @@
         <v>0.4212</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.6669</v>
       </c>
     </row>
     <row r="26">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E26" t="n">
         <v>0.9755</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2884</v>
+        <v>0.2883</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.6387</v>
       </c>
     </row>
     <row r="27">
@@ -1194,17 +1194,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9618</v>
+        <v>0.9619</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3134</v>
+        <v>0.3136</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.6435999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1223,17 +1223,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9456</v>
+        <v>0.9459</v>
       </c>
       <c r="F28" t="n">
         <v>0.3598</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.6508</v>
       </c>
     </row>
     <row r="29">
@@ -1252,17 +1252,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.949</v>
+        <v>0.9527</v>
       </c>
       <c r="F29" t="n">
-        <v>0.327</v>
+        <v>0.3261</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.6552</v>
       </c>
     </row>
     <row r="30">
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9392</v>
+        <v>0.9389</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3678</v>
+        <v>0.3675</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.6585</v>
       </c>
     </row>
     <row r="31">
@@ -1310,17 +1310,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9593</v>
+        <v>0.9542</v>
       </c>
       <c r="F31" t="n">
-        <v>0.315</v>
+        <v>0.319</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.6636</v>
       </c>
     </row>
     <row r="32">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9159</v>
+        <v>0.9016</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3994</v>
+        <v>0.4155</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.6636</v>
       </c>
     </row>
     <row r="33">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.949</v>
+        <v>0.9495</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3299</v>
+        <v>0.329</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="34">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9488</v>
+        <v>0.9487</v>
       </c>
       <c r="F34" t="n">
         <v>0.3775</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.6407</v>
       </c>
     </row>
     <row r="35">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1436,7 +1436,7 @@
         <v>0.3851</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.6503</v>
       </c>
     </row>
     <row r="36">
@@ -1455,17 +1455,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9714</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3109</v>
+        <v>0.3322</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.6438</v>
       </c>
     </row>
     <row r="37">
@@ -1484,17 +1484,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9648</v>
+        <v>0.9361</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2997</v>
+        <v>0.3929</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.6481</v>
       </c>
     </row>
     <row r="38">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.952</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3443</v>
+        <v>0.3457</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.6414</v>
       </c>
     </row>
     <row r="39">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9389</v>
+        <v>0.9398</v>
       </c>
       <c r="F39" t="n">
         <v>0.3685</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.6491</v>
       </c>
     </row>
     <row r="40">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9485</v>
+        <v>0.9487</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3632</v>
+        <v>0.3628</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.6512</v>
       </c>
     </row>
     <row r="41">
@@ -1600,17 +1600,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9482</v>
+        <v>0.9483</v>
       </c>
       <c r="F41" t="n">
         <v>0.3778</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.6403</v>
       </c>
     </row>
     <row r="42">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1639,7 +1639,7 @@
         <v>0.3848</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.6495</v>
       </c>
     </row>
     <row r="43">
@@ -1658,17 +1658,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9777</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2866</v>
+        <v>0.2867</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>0.6452</v>
       </c>
     </row>
     <row r="44">
@@ -1687,17 +1687,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9651</v>
+        <v>0.9792</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2995</v>
+        <v>0.2526</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="45">
@@ -1716,17 +1716,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9586</v>
+        <v>0.9294</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3245</v>
+        <v>0.3947</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>0.6456</v>
       </c>
     </row>
     <row r="46">
@@ -1745,17 +1745,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9564</v>
+        <v>0.9568</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3495</v>
+        <v>0.3493</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>0.6544</v>
       </c>
     </row>
     <row r="47">
@@ -1774,17 +1774,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9249000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="F47" t="n">
         <v>0.3989</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.6589</v>
       </c>
     </row>
     <row r="48">
@@ -1803,17 +1803,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9717</v>
+        <v>0.972</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3128</v>
+        <v>0.312</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.6453</v>
       </c>
     </row>
     <row r="49">
@@ -1832,17 +1832,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9835</v>
+        <v>0.9437</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2491</v>
+        <v>0.3859</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="50">
@@ -1861,17 +1861,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9021</v>
+        <v>0.9019</v>
       </c>
       <c r="F50" t="n">
         <v>0.3996</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>0.6497000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1900,7 +1900,7 @@
         <v>0.4268</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>0.6731</v>
       </c>
     </row>
     <row r="52">
@@ -1919,17 +1919,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.8687</v>
+        <v>0.8688</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4279</v>
+        <v>0.4278</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="53">
@@ -1948,17 +1948,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.9121</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3775</v>
+        <v>0.3777</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="54">
@@ -1977,17 +1977,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.908</v>
+        <v>0.9085</v>
       </c>
       <c r="F54" t="n">
         <v>0.3913</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>0.668</v>
       </c>
     </row>
     <row r="55">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.9328</v>
+        <v>0.9329</v>
       </c>
       <c r="F55" t="n">
-        <v>0.3452</v>
+        <v>0.3451</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>0.6433</v>
       </c>
     </row>
     <row r="56">
@@ -2035,17 +2035,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9306</v>
+        <v>0.9307</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3624</v>
+        <v>0.3622</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>0.6378</v>
       </c>
     </row>
     <row r="57">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9581</v>
+        <v>0.9589</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2954</v>
+        <v>0.2948</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>0.6489</v>
       </c>
     </row>
     <row r="58">
@@ -2093,17 +2093,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8182</v>
+        <v>0.8183</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4421</v>
+        <v>0.4422</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>0.6885</v>
       </c>
     </row>
     <row r="59">
@@ -2122,17 +2122,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E59" t="n">
         <v>0.8193</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4422</v>
+        <v>0.4423</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>0.6895</v>
       </c>
     </row>
     <row r="60">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.9086</v>
+        <v>0.8174</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3657</v>
+        <v>0.4427</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.8925</v>
+        <v>0.8928</v>
       </c>
       <c r="F61" t="n">
-        <v>0.3817</v>
+        <v>0.3816</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>0.6897</v>
       </c>
     </row>
     <row r="62">
@@ -2209,17 +2209,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.9194</v>
+        <v>0.9191</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3418</v>
+        <v>0.3428</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>0.6569</v>
       </c>
     </row>
     <row r="63">
@@ -2238,17 +2238,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.9089</v>
+        <v>0.9097</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3618</v>
+        <v>0.3619</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>0.6553</v>
       </c>
     </row>
     <row r="64">
@@ -2267,17 +2267,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8591</v>
+        <v>0.8593</v>
       </c>
       <c r="F64" t="n">
-        <v>0.4102</v>
+        <v>0.4101</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>0.6539</v>
       </c>
     </row>
     <row r="65">
@@ -2296,17 +2296,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.9049</v>
+        <v>0.9048</v>
       </c>
       <c r="F65" t="n">
-        <v>0.366</v>
+        <v>0.3665</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>0.6572</v>
       </c>
     </row>
     <row r="66">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9465</v>
+        <v>0.9455</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3272</v>
+        <v>0.3278</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>0.6496</v>
       </c>
     </row>
     <row r="67">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9062</v>
+        <v>0.9065</v>
       </c>
       <c r="F67" t="n">
         <v>0.3937</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>0.6459</v>
       </c>
     </row>
     <row r="68">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9385</v>
+        <v>0.944</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3468</v>
+        <v>0.3265</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>0.6483</v>
       </c>
     </row>
     <row r="69">
@@ -2412,17 +2412,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9445</v>
+        <v>0.9435</v>
       </c>
       <c r="F69" t="n">
-        <v>0.3406</v>
+        <v>0.341</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>0.6653</v>
       </c>
     </row>
     <row r="70">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9418</v>
+        <v>0.9414</v>
       </c>
       <c r="F70" t="n">
-        <v>0.339</v>
+        <v>0.3393</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>0.6645</v>
       </c>
     </row>
     <row r="71">
@@ -2470,17 +2470,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9317</v>
+        <v>0.9319</v>
       </c>
       <c r="F71" t="n">
         <v>0.3795</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>0.6538</v>
       </c>
     </row>
     <row r="72">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2509,7 +2509,7 @@
         <v>0.3686</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>0.6637</v>
       </c>
     </row>
     <row r="73">
@@ -2528,17 +2528,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9438</v>
+        <v>0.9436</v>
       </c>
       <c r="F73" t="n">
         <v>0.385</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>0.6549</v>
       </c>
     </row>
     <row r="74">
@@ -2557,17 +2557,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9399</v>
+        <v>0.9257</v>
       </c>
       <c r="F74" t="n">
-        <v>0.382</v>
+        <v>0.4141</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>0.6673</v>
       </c>
     </row>
     <row r="75">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9186</v>
+        <v>0.9183</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3719</v>
+        <v>0.372</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>0.6833</v>
       </c>
     </row>
     <row r="76">
@@ -2615,17 +2615,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9186</v>
+        <v>0.9183</v>
       </c>
       <c r="F76" t="n">
-        <v>0.3719</v>
+        <v>0.372</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>0.6833</v>
       </c>
     </row>
     <row r="77">
@@ -2644,17 +2644,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8974</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="F77" t="n">
         <v>0.3732</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -2673,17 +2673,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.9045</v>
+        <v>0.8993</v>
       </c>
       <c r="F78" t="n">
-        <v>0.366</v>
+        <v>0.3727</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>0.6817</v>
       </c>
     </row>
     <row r="79">
@@ -2702,17 +2702,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.8994</v>
       </c>
       <c r="F79" t="n">
-        <v>0.3715</v>
+        <v>0.3718</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>0.6818</v>
       </c>
     </row>
     <row r="80">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8995</v>
+        <v>0.8991</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3724</v>
+        <v>0.3729</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>0.6815</v>
       </c>
     </row>
     <row r="81">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.9212</v>
+        <v>0.8689</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3445</v>
+        <v>0.4105</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>0.6594</v>
       </c>
     </row>
     <row r="82">
@@ -2789,17 +2789,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.8651</v>
+        <v>0.8648</v>
       </c>
       <c r="F82" t="n">
-        <v>0.4118</v>
+        <v>0.4119</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>0.6603</v>
       </c>
     </row>
     <row r="83">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9153</v>
+        <v>0.9152</v>
       </c>
       <c r="F83" t="n">
-        <v>0.3731</v>
+        <v>0.3729</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>0.6851</v>
       </c>
     </row>
     <row r="84">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9134</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="F84" t="n">
-        <v>0.3741</v>
+        <v>0.3561</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="85">
@@ -2876,17 +2876,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9153</v>
+        <v>0.9324</v>
       </c>
       <c r="F85" t="n">
-        <v>0.3732</v>
+        <v>0.3535</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>0.6855</v>
       </c>
     </row>
     <row r="86">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.976</v>
+        <v>0.9762</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2938</v>
+        <v>0.2931</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>0.6588000000000001</v>
       </c>
     </row>
     <row r="87">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9595</v>
+        <v>0.9593</v>
       </c>
       <c r="F87" t="n">
-        <v>0.3501</v>
+        <v>0.3502</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.6614</v>
       </c>
     </row>
     <row r="88">
@@ -2963,17 +2963,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9559</v>
+        <v>0.9555</v>
       </c>
       <c r="F88" t="n">
-        <v>0.3345</v>
+        <v>0.3349</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>0.6551</v>
       </c>
     </row>
     <row r="89">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9504</v>
+        <v>0.9493</v>
       </c>
       <c r="F89" t="n">
-        <v>0.3331</v>
+        <v>0.3347</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>0.6575</v>
       </c>
     </row>
     <row r="90">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9778</v>
+        <v>0.9492</v>
       </c>
       <c r="F90" t="n">
-        <v>0.2863</v>
+        <v>0.3693</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>0.6453</v>
       </c>
     </row>
     <row r="91">
@@ -3050,17 +3050,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9792</v>
       </c>
       <c r="F91" t="n">
-        <v>0.2994</v>
+        <v>0.2526</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>0.6464</v>
       </c>
     </row>
     <row r="92">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9559</v>
+        <v>0.9555</v>
       </c>
       <c r="F92" t="n">
-        <v>0.3345</v>
+        <v>0.3349</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>0.6551</v>
       </c>
     </row>
     <row r="93">
@@ -3108,17 +3108,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9792</v>
       </c>
       <c r="F93" t="n">
-        <v>0.2994</v>
+        <v>0.2526</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>0.6464</v>
       </c>
     </row>
     <row r="94">
@@ -3137,17 +3137,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9495</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="F94" t="n">
-        <v>0.2601</v>
+        <v>0.3401</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>0.6069</v>
       </c>
     </row>
     <row r="95">
@@ -3166,17 +3166,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.7642</v>
+        <v>0.7641</v>
       </c>
       <c r="F95" t="n">
-        <v>0.4541</v>
+        <v>0.4542</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>0.6499</v>
       </c>
     </row>
     <row r="96">
@@ -3195,17 +3195,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.8995</v>
+        <v>0.8998</v>
       </c>
       <c r="F96" t="n">
-        <v>0.3316</v>
+        <v>0.3309</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>0.6128</v>
       </c>
     </row>
     <row r="97">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9005</v>
+        <v>0.8914</v>
       </c>
       <c r="F97" t="n">
-        <v>0.3299</v>
+        <v>0.3457</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>0.6099</v>
       </c>
     </row>
     <row r="98">
@@ -3253,17 +3253,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9346</v>
+        <v>0.9341</v>
       </c>
       <c r="F98" t="n">
-        <v>0.3045</v>
+        <v>0.3053</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>0.5972</v>
       </c>
     </row>
     <row r="99">
@@ -3282,17 +3282,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.925</v>
+        <v>0.9254</v>
       </c>
       <c r="F99" t="n">
-        <v>0.3075</v>
+        <v>0.3071</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="100">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9286</v>
+        <v>0.9293</v>
       </c>
       <c r="F100" t="n">
-        <v>0.2997</v>
+        <v>0.2993</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>0.6016</v>
       </c>
     </row>
     <row r="101">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9156</v>
+        <v>0.9154</v>
       </c>
       <c r="F101" t="n">
-        <v>0.3204</v>
+        <v>0.3207</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>0.6052999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9423</v>
+        <v>0.9053</v>
       </c>
       <c r="F102" t="n">
-        <v>0.287</v>
+        <v>0.3387</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>0.6064000000000001</v>
       </c>
     </row>
     <row r="103">
@@ -3398,17 +3398,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9719</v>
+        <v>0.9201</v>
       </c>
       <c r="F103" t="n">
-        <v>0.2353</v>
+        <v>0.3392</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>0.6011</v>
       </c>
     </row>
     <row r="104">
@@ -3427,17 +3427,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9734</v>
+        <v>0.9443</v>
       </c>
       <c r="F104" t="n">
-        <v>0.2345</v>
+        <v>0.2863</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>0.5928</v>
       </c>
     </row>
     <row r="105">
@@ -3456,17 +3456,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9338</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="F105" t="n">
-        <v>0.3002</v>
+        <v>0.2559</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>0.5957</v>
       </c>
     </row>
     <row r="106">
@@ -3485,17 +3485,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9324</v>
+        <v>0.9333</v>
       </c>
       <c r="F106" t="n">
-        <v>0.2971</v>
+        <v>0.2965</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>0.5904</v>
       </c>
     </row>
     <row r="107">
@@ -3514,17 +3514,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.8529</v>
+        <v>0.9264</v>
       </c>
       <c r="F107" t="n">
-        <v>0.3932</v>
+        <v>0.3052</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>0.6061</v>
       </c>
     </row>
     <row r="108">
@@ -3543,17 +3543,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9375</v>
+        <v>0.9369</v>
       </c>
       <c r="F108" t="n">
-        <v>0.3208</v>
+        <v>0.3217</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>0.6129</v>
       </c>
     </row>
     <row r="109">
@@ -3572,17 +3572,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.957</v>
+        <v>0.9727</v>
       </c>
       <c r="F109" t="n">
-        <v>0.2773</v>
+        <v>0.2378</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="110">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9251</v>
+        <v>0.9548</v>
       </c>
       <c r="F110" t="n">
-        <v>0.3118</v>
+        <v>0.2592</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>0.5969</v>
       </c>
     </row>
     <row r="111">
@@ -3630,17 +3630,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.9282</v>
       </c>
       <c r="F111" t="n">
-        <v>0.3074</v>
+        <v>0.3072</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>0.5904</v>
       </c>
     </row>
     <row r="112">
@@ -3659,17 +3659,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9735</v>
+        <v>0.8921</v>
       </c>
       <c r="F112" t="n">
-        <v>0.2397</v>
+        <v>0.3779</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>0.6136</v>
       </c>
     </row>
     <row r="113">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9555</v>
+        <v>0.9559</v>
       </c>
       <c r="F113" t="n">
-        <v>0.2795</v>
+        <v>0.2797</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>0.6102</v>
       </c>
     </row>
     <row r="114">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9263</v>
+        <v>0.9267</v>
       </c>
       <c r="F114" t="n">
-        <v>0.3114</v>
+        <v>0.3107</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>0.5982</v>
       </c>
     </row>
     <row r="115">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.927</v>
       </c>
       <c r="F115" t="n">
-        <v>0.3076</v>
+        <v>0.3073</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>0.5899</v>
       </c>
     </row>
     <row r="116">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9015</v>
+        <v>0.9012</v>
       </c>
       <c r="F116" t="n">
-        <v>0.3442</v>
+        <v>0.3443</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>0.6116</v>
       </c>
     </row>
     <row r="117">
@@ -3804,17 +3804,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.9085</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="F117" t="n">
-        <v>0.3335</v>
+        <v>0.3982</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>0.6117</v>
       </c>
     </row>
     <row r="118">
@@ -3833,17 +3833,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9338</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="F118" t="n">
-        <v>0.3002</v>
+        <v>0.2559</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>0.5957</v>
       </c>
     </row>
     <row r="119">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9555</v>
+        <v>0.9559</v>
       </c>
       <c r="F119" t="n">
-        <v>0.2795</v>
+        <v>0.2797</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>0.6102</v>
       </c>
     </row>
     <row r="120">
@@ -3891,17 +3891,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.8718</v>
+        <v>0.8717</v>
       </c>
       <c r="F120" t="n">
-        <v>0.366</v>
+        <v>0.3661</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>0.6317</v>
       </c>
     </row>
     <row r="121">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.8718</v>
+        <v>0.8717</v>
       </c>
       <c r="F121" t="n">
-        <v>0.366</v>
+        <v>0.3661</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>0.6317</v>
       </c>
     </row>
     <row r="122">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9223</v>
+        <v>0.9226</v>
       </c>
       <c r="F122" t="n">
-        <v>0.3144</v>
+        <v>0.3141</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>0.6015</v>
       </c>
     </row>
     <row r="123">
@@ -3978,17 +3978,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9555</v>
+        <v>0.9558</v>
       </c>
       <c r="F123" t="n">
-        <v>0.2795</v>
+        <v>0.2797</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>0.6103</v>
       </c>
     </row>
     <row r="124">
@@ -4007,17 +4007,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9411</v>
+        <v>0.9115</v>
       </c>
       <c r="F124" t="n">
-        <v>0.3031</v>
+        <v>0.3414</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>0.6004</v>
       </c>
     </row>
     <row r="125">
@@ -4036,17 +4036,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9046</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="F125" t="n">
-        <v>0.3257</v>
+        <v>0.3264</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>0.6066</v>
       </c>
     </row>
     <row r="126">
@@ -4065,17 +4065,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9628</v>
+        <v>0.9536</v>
       </c>
       <c r="F126" t="n">
-        <v>0.2653</v>
+        <v>0.2837</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>0.6254</v>
       </c>
     </row>
     <row r="127">
@@ -4094,17 +4094,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.8697</v>
       </c>
       <c r="F127" t="n">
-        <v>0.3942</v>
+        <v>0.394</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>0.6555</v>
       </c>
     </row>
     <row r="128">
@@ -4123,17 +4123,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.9111</v>
+        <v>0.9115</v>
       </c>
       <c r="F128" t="n">
-        <v>0.3507</v>
+        <v>0.3506</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>0.6309</v>
       </c>
     </row>
     <row r="129">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.9244</v>
+        <v>0.9719</v>
       </c>
       <c r="F129" t="n">
-        <v>0.3286</v>
+        <v>0.2391</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>0.6321</v>
       </c>
     </row>
     <row r="130">
@@ -4181,17 +4181,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.9225</v>
+        <v>0.9717</v>
       </c>
       <c r="F130" t="n">
-        <v>0.3321</v>
+        <v>0.2391</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>0.6284999999999999</v>
       </c>
     </row>
     <row r="131">
@@ -4210,17 +4210,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.9196</v>
+        <v>0.9719</v>
       </c>
       <c r="F131" t="n">
-        <v>0.3359</v>
+        <v>0.2389</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>0.6253</v>
       </c>
     </row>
     <row r="132">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.911</v>
+        <v>0.973</v>
       </c>
       <c r="F132" t="n">
-        <v>0.3507</v>
+        <v>0.2408</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>0.6336000000000001</v>
       </c>
     </row>
     <row r="133">
@@ -4268,17 +4268,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.9227</v>
+        <v>0.9216</v>
       </c>
       <c r="F133" t="n">
-        <v>0.3318</v>
+        <v>0.3325</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>0.6304999999999999</v>
       </c>
     </row>
     <row r="134">
@@ -4297,17 +4297,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.9107</v>
+        <v>0.9112</v>
       </c>
       <c r="F134" t="n">
-        <v>0.3498</v>
+        <v>0.3505</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>0.6316000000000001</v>
       </c>
     </row>
     <row r="135">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.9121</v>
+        <v>0.9185</v>
       </c>
       <c r="F135" t="n">
-        <v>0.3501</v>
+        <v>0.3332</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
     </row>
     <row r="136">
@@ -4355,17 +4355,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.9208</v>
+        <v>0.9214</v>
       </c>
       <c r="F136" t="n">
-        <v>0.335</v>
+        <v>0.3346</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>0.6261</v>
       </c>
     </row>
     <row r="137">
@@ -4384,17 +4384,17 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9705</v>
+        <v>0.975</v>
       </c>
       <c r="F137" t="n">
-        <v>0.26</v>
+        <v>0.2426</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>0.6379</v>
       </c>
     </row>
     <row r="138">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9621</v>
+        <v>0.9798</v>
       </c>
       <c r="F138" t="n">
-        <v>0.2983</v>
+        <v>0.2421</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>0.6408</v>
       </c>
     </row>
     <row r="139">
@@ -4442,17 +4442,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9649</v>
+        <v>0.9658</v>
       </c>
       <c r="F139" t="n">
-        <v>0.2759</v>
+        <v>0.2738</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>0.6328</v>
       </c>
     </row>
     <row r="140">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.9798</v>
+        <v>0.98</v>
       </c>
       <c r="F140" t="n">
-        <v>0.2833</v>
+        <v>0.283</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>0.6504</v>
       </c>
     </row>
     <row r="141">
@@ -4500,17 +4500,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9816</v>
+        <v>0.9326</v>
       </c>
       <c r="F141" t="n">
-        <v>0.2651</v>
+        <v>0.3972</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>0.6482</v>
       </c>
     </row>
     <row r="142">
@@ -4529,17 +4529,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9621</v>
+        <v>0.9798</v>
       </c>
       <c r="F142" t="n">
-        <v>0.2983</v>
+        <v>0.2421</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>0.6408</v>
       </c>
     </row>
     <row r="143">
@@ -4558,17 +4558,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.9669</v>
+        <v>0.9465</v>
       </c>
       <c r="F143" t="n">
-        <v>0.2619</v>
+        <v>0.3112</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="144">
@@ -4587,17 +4587,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9399</v>
+        <v>0.9442</v>
       </c>
       <c r="F144" t="n">
-        <v>0.3153</v>
+        <v>0.3097</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>0.6368</v>
       </c>
     </row>
     <row r="145">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.9816</v>
+        <v>0.9326</v>
       </c>
       <c r="F145" t="n">
-        <v>0.2651</v>
+        <v>0.3972</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>0.6482</v>
       </c>
     </row>
     <row r="146">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.8697</v>
+        <v>0.8701</v>
       </c>
       <c r="F146" t="n">
-        <v>0.3945</v>
+        <v>0.3943</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>0.6539</v>
       </c>
     </row>
     <row r="147">
@@ -4674,17 +4674,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.8665</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="F147" t="n">
-        <v>0.3965</v>
+        <v>0.3963</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>0.6535</v>
       </c>
     </row>
     <row r="148">
@@ -4703,17 +4703,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.866</v>
+        <v>0.8659</v>
       </c>
       <c r="F148" t="n">
-        <v>0.3972</v>
+        <v>0.3974</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>0.6534</v>
       </c>
     </row>
     <row r="149">
@@ -4732,17 +4732,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.8676</v>
+        <v>0.8677</v>
       </c>
       <c r="F149" t="n">
-        <v>0.394</v>
+        <v>0.3942</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>0.6509</v>
       </c>
     </row>
     <row r="150">
@@ -4761,17 +4761,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.8686</v>
+        <v>0.8691</v>
       </c>
       <c r="F150" t="n">
-        <v>0.3943</v>
+        <v>0.3939</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>0.6567</v>
       </c>
     </row>
     <row r="151">
@@ -4790,17 +4790,17 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.8681</v>
+        <v>0.8687</v>
       </c>
       <c r="F151" t="n">
-        <v>0.3948</v>
+        <v>0.3942</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="152">
@@ -4819,17 +4819,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.8689</v>
+        <v>0.8692</v>
       </c>
       <c r="F152" t="n">
-        <v>0.3943</v>
+        <v>0.3944</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>0.6553</v>
       </c>
     </row>
     <row r="153">
@@ -4848,17 +4848,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.8683999999999999</v>
+        <v>0.8688</v>
       </c>
       <c r="F153" t="n">
-        <v>0.3944</v>
+        <v>0.3942</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>0.6544</v>
       </c>
     </row>
     <row r="154">
@@ -4877,17 +4877,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.8683999999999999</v>
       </c>
       <c r="F154" t="n">
-        <v>0.3949</v>
+        <v>0.3945</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>0.6545</v>
       </c>
     </row>
     <row r="155">
@@ -4906,17 +4906,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.8929</v>
+        <v>0.8927</v>
       </c>
       <c r="F155" t="n">
-        <v>0.3842</v>
+        <v>0.384</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>0.6571</v>
       </c>
     </row>
     <row r="156">
@@ -4935,17 +4935,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.8959</v>
+        <v>0.896</v>
       </c>
       <c r="F156" t="n">
-        <v>0.3779</v>
+        <v>0.3781</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>0.6591</v>
       </c>
     </row>
     <row r="157">
@@ -4964,17 +4964,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.9529</v>
+        <v>0.9527</v>
       </c>
       <c r="F157" t="n">
-        <v>0.2995</v>
+        <v>0.2993</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>0.6579</v>
       </c>
     </row>
     <row r="158">
@@ -4993,17 +4993,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.924</v>
+        <v>0.9245</v>
       </c>
       <c r="F158" t="n">
         <v>0.3585</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>0.6384</v>
       </c>
     </row>
     <row r="159">
@@ -5022,17 +5022,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.9721</v>
       </c>
       <c r="F159" t="n">
-        <v>0.3856</v>
+        <v>0.2489</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>0.6481</v>
       </c>
     </row>
     <row r="160">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.9045</v>
+        <v>0.9039</v>
       </c>
       <c r="F160" t="n">
-        <v>0.3616</v>
+        <v>0.3621</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>0.6501</v>
       </c>
     </row>
     <row r="161">
@@ -5080,17 +5080,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.9013</v>
+        <v>0.9014</v>
       </c>
       <c r="F161" t="n">
-        <v>0.3625</v>
+        <v>0.3629</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>0.6472</v>
       </c>
     </row>
     <row r="162">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.9719</v>
+        <v>0.896</v>
       </c>
       <c r="F162" t="n">
-        <v>0.2507</v>
+        <v>0.3822</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>0.6526999999999999</v>
       </c>
     </row>
     <row r="163">
@@ -5138,17 +5138,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9788</v>
+        <v>0.8914</v>
       </c>
       <c r="F163" t="n">
-        <v>0.2472</v>
+        <v>0.4072</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>0.6548</v>
       </c>
     </row>
     <row r="164">
@@ -5167,17 +5167,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.98</v>
+        <v>0.9802</v>
       </c>
       <c r="F164" t="n">
-        <v>0.2829</v>
+        <v>0.2827</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>0.6502</v>
       </c>
     </row>
     <row r="165">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9046</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="F165" t="n">
-        <v>0.3257</v>
+        <v>0.3264</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>0.6066</v>
       </c>
     </row>
     <row r="166">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.7638</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="F166" t="n">
         <v>0.4548</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>0.6511</v>
       </c>
     </row>
     <row r="167">
@@ -5254,17 +5254,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.957</v>
+        <v>0.9574</v>
       </c>
       <c r="F167" t="n">
-        <v>0.3053</v>
+        <v>0.3041</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>0.6328</v>
       </c>
     </row>
     <row r="168">
@@ -5283,17 +5283,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9641</v>
+        <v>0.9503</v>
       </c>
       <c r="F168" t="n">
-        <v>0.3395</v>
+        <v>0.3596</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>0.6441</v>
       </c>
     </row>
     <row r="169">
@@ -5312,17 +5312,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9673</v>
+        <v>0.9671</v>
       </c>
       <c r="F169" t="n">
-        <v>0.2827</v>
+        <v>0.2836</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>0.6363</v>
       </c>
     </row>
     <row r="170">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.9472</v>
+        <v>0.9473</v>
       </c>
       <c r="F170" t="n">
-        <v>0.3798</v>
+        <v>0.3799</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>0.6548</v>
       </c>
     </row>
     <row r="171">
@@ -5370,17 +5370,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E171" t="n">
         <v>0.9393</v>
       </c>
       <c r="F171" t="n">
-        <v>0.3868</v>
+        <v>0.3869</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>0.6474</v>
       </c>
     </row>
     <row r="172">
@@ -5399,17 +5399,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9341</v>
+        <v>0.9771</v>
       </c>
       <c r="F172" t="n">
-        <v>0.3366</v>
+        <v>0.2415</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>0.6553</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C18.1n7/RANDOMSEARCH_DETAILS_C18.1n7.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C18.1n7/RANDOMSEARCH_DETAILS_C18.1n7.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,10 +444,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>RMSEC</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>RMSECV</t>
         </is>
@@ -476,9 +481,12 @@
         <v>0.9347</v>
       </c>
       <c r="F2" t="n">
+        <v>1.9834</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.3655</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>0.6421</v>
       </c>
     </row>
@@ -505,9 +513,12 @@
         <v>0.9686</v>
       </c>
       <c r="F3" t="n">
+        <v>1.9926</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.3067</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>0.6451</v>
       </c>
     </row>
@@ -534,9 +545,12 @@
         <v>0.8977000000000001</v>
       </c>
       <c r="F4" t="n">
+        <v>1.8785</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.3401</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>0.6069</v>
       </c>
     </row>
@@ -563,9 +577,12 @@
         <v>0.8998</v>
       </c>
       <c r="F5" t="n">
+        <v>2.1425</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.3772</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>0.6921</v>
       </c>
     </row>
@@ -592,9 +609,12 @@
         <v>0.8186</v>
       </c>
       <c r="F6" t="n">
+        <v>2.1309</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.4415</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>0.6885</v>
       </c>
     </row>
@@ -621,9 +641,12 @@
         <v>0.919</v>
       </c>
       <c r="F7" t="n">
+        <v>2.0884</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.3531</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>0.6755</v>
       </c>
     </row>
@@ -650,9 +673,12 @@
         <v>0.9349</v>
       </c>
       <c r="F8" t="n">
+        <v>2.0429</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.3493</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>0.6612</v>
       </c>
     </row>
@@ -679,9 +705,12 @@
         <v>0.974</v>
       </c>
       <c r="F9" t="n">
+        <v>1.9675</v>
+      </c>
+      <c r="G9" t="n">
         <v>0.2779</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>0.6369</v>
       </c>
     </row>
@@ -708,9 +737,12 @@
         <v>0.9392</v>
       </c>
       <c r="F10" t="n">
+        <v>2.0429</v>
+      </c>
+      <c r="G10" t="n">
         <v>0.3332</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>0.6612</v>
       </c>
     </row>
@@ -737,9 +769,12 @@
         <v>0.9277</v>
       </c>
       <c r="F11" t="n">
+        <v>2.0533</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.3526</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>0.6645</v>
       </c>
     </row>
@@ -766,9 +801,12 @@
         <v>0.9257</v>
       </c>
       <c r="F12" t="n">
+        <v>2.0653</v>
+      </c>
+      <c r="G12" t="n">
         <v>0.3544</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>0.6683</v>
       </c>
     </row>
@@ -795,9 +833,12 @@
         <v>0.9537</v>
       </c>
       <c r="F13" t="n">
+        <v>2.052</v>
+      </c>
+      <c r="G13" t="n">
         <v>0.3039</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>0.6641</v>
       </c>
     </row>
@@ -824,9 +865,12 @@
         <v>0.9286</v>
       </c>
       <c r="F14" t="n">
+        <v>2.0509</v>
+      </c>
+      <c r="G14" t="n">
         <v>0.3494</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>0.6637999999999999</v>
       </c>
     </row>
@@ -853,9 +897,12 @@
         <v>0.9553</v>
       </c>
       <c r="F15" t="n">
+        <v>2.0581</v>
+      </c>
+      <c r="G15" t="n">
         <v>0.3035</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>0.666</v>
       </c>
     </row>
@@ -882,9 +929,12 @@
         <v>0.953</v>
       </c>
       <c r="F16" t="n">
+        <v>2.0559</v>
+      </c>
+      <c r="G16" t="n">
         <v>0.3049</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>0.6653</v>
       </c>
     </row>
@@ -911,9 +961,12 @@
         <v>0.9235</v>
       </c>
       <c r="F17" t="n">
+        <v>2.0574</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.3532</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>0.6657999999999999</v>
       </c>
     </row>
@@ -940,9 +993,12 @@
         <v>0.9623</v>
       </c>
       <c r="F18" t="n">
+        <v>1.988</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.3175</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>0.6435999999999999</v>
       </c>
     </row>
@@ -969,9 +1025,12 @@
         <v>0.9510999999999999</v>
       </c>
       <c r="F19" t="n">
+        <v>1.9993</v>
+      </c>
+      <c r="G19" t="n">
         <v>0.326</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>0.6473</v>
       </c>
     </row>
@@ -998,9 +1057,12 @@
         <v>0.9038</v>
       </c>
       <c r="F20" t="n">
+        <v>2.0544</v>
+      </c>
+      <c r="G20" t="n">
         <v>0.4167</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>0.6647999999999999</v>
       </c>
     </row>
@@ -1027,9 +1089,12 @@
         <v>0.9491000000000001</v>
       </c>
       <c r="F21" t="n">
+        <v>2.0467</v>
+      </c>
+      <c r="G21" t="n">
         <v>0.3311</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>0.6624</v>
       </c>
     </row>
@@ -1056,9 +1121,12 @@
         <v>0.9454</v>
       </c>
       <c r="F22" t="n">
+        <v>2.0441</v>
+      </c>
+      <c r="G22" t="n">
         <v>0.3311</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>0.6616</v>
       </c>
     </row>
@@ -1085,9 +1153,12 @@
         <v>0.9452</v>
       </c>
       <c r="F23" t="n">
+        <v>2.0461</v>
+      </c>
+      <c r="G23" t="n">
         <v>0.3378</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>0.6622</v>
       </c>
     </row>
@@ -1114,9 +1185,12 @@
         <v>0.8882</v>
       </c>
       <c r="F24" t="n">
+        <v>2.0554</v>
+      </c>
+      <c r="G24" t="n">
         <v>0.424</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>0.6652</v>
       </c>
     </row>
@@ -1143,9 +1217,12 @@
         <v>0.8883</v>
       </c>
       <c r="F25" t="n">
+        <v>2.0611</v>
+      </c>
+      <c r="G25" t="n">
         <v>0.4212</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>0.6669</v>
       </c>
     </row>
@@ -1172,9 +1249,12 @@
         <v>0.9755</v>
       </c>
       <c r="F26" t="n">
+        <v>1.973</v>
+      </c>
+      <c r="G26" t="n">
         <v>0.2883</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>0.6387</v>
       </c>
     </row>
@@ -1201,9 +1281,12 @@
         <v>0.9619</v>
       </c>
       <c r="F27" t="n">
+        <v>1.9881</v>
+      </c>
+      <c r="G27" t="n">
         <v>0.3136</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>0.6435999999999999</v>
       </c>
     </row>
@@ -1230,9 +1313,12 @@
         <v>0.9459</v>
       </c>
       <c r="F28" t="n">
+        <v>2.0103</v>
+      </c>
+      <c r="G28" t="n">
         <v>0.3598</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>0.6508</v>
       </c>
     </row>
@@ -1259,9 +1345,12 @@
         <v>0.9527</v>
       </c>
       <c r="F29" t="n">
+        <v>2.0239</v>
+      </c>
+      <c r="G29" t="n">
         <v>0.3261</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>0.6552</v>
       </c>
     </row>
@@ -1288,9 +1377,12 @@
         <v>0.9389</v>
       </c>
       <c r="F30" t="n">
+        <v>2.0345</v>
+      </c>
+      <c r="G30" t="n">
         <v>0.3675</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>0.6585</v>
       </c>
     </row>
@@ -1317,9 +1409,12 @@
         <v>0.9542</v>
       </c>
       <c r="F31" t="n">
+        <v>2.0503</v>
+      </c>
+      <c r="G31" t="n">
         <v>0.319</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>0.6636</v>
       </c>
     </row>
@@ -1346,9 +1441,12 @@
         <v>0.9016</v>
       </c>
       <c r="F32" t="n">
+        <v>2.0505</v>
+      </c>
+      <c r="G32" t="n">
         <v>0.4155</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>0.6636</v>
       </c>
     </row>
@@ -1375,9 +1473,12 @@
         <v>0.9495</v>
       </c>
       <c r="F33" t="n">
+        <v>2.0272</v>
+      </c>
+      <c r="G33" t="n">
         <v>0.329</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>0.6562</v>
       </c>
     </row>
@@ -1404,9 +1505,12 @@
         <v>0.9487</v>
       </c>
       <c r="F34" t="n">
+        <v>1.9792</v>
+      </c>
+      <c r="G34" t="n">
         <v>0.3775</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>0.6407</v>
       </c>
     </row>
@@ -1433,9 +1537,12 @@
         <v>0.9437</v>
       </c>
       <c r="F35" t="n">
+        <v>2.0088</v>
+      </c>
+      <c r="G35" t="n">
         <v>0.3851</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>0.6503</v>
       </c>
     </row>
@@ -1462,9 +1569,12 @@
         <v>0.9671999999999999</v>
       </c>
       <c r="F36" t="n">
+        <v>1.9887</v>
+      </c>
+      <c r="G36" t="n">
         <v>0.3322</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>0.6438</v>
       </c>
     </row>
@@ -1491,9 +1601,12 @@
         <v>0.9361</v>
       </c>
       <c r="F37" t="n">
+        <v>2.002</v>
+      </c>
+      <c r="G37" t="n">
         <v>0.3929</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>0.6481</v>
       </c>
     </row>
@@ -1520,9 +1633,12 @@
         <v>0.952</v>
       </c>
       <c r="F38" t="n">
+        <v>1.9814</v>
+      </c>
+      <c r="G38" t="n">
         <v>0.3457</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>0.6414</v>
       </c>
     </row>
@@ -1549,9 +1665,12 @@
         <v>0.9398</v>
       </c>
       <c r="F39" t="n">
+        <v>2.0049</v>
+      </c>
+      <c r="G39" t="n">
         <v>0.3685</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>0.6491</v>
       </c>
     </row>
@@ -1578,9 +1697,12 @@
         <v>0.9487</v>
       </c>
       <c r="F40" t="n">
+        <v>2.0117</v>
+      </c>
+      <c r="G40" t="n">
         <v>0.3628</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>0.6512</v>
       </c>
     </row>
@@ -1607,9 +1729,12 @@
         <v>0.9483</v>
       </c>
       <c r="F41" t="n">
+        <v>1.9781</v>
+      </c>
+      <c r="G41" t="n">
         <v>0.3778</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>0.6403</v>
       </c>
     </row>
@@ -1636,9 +1761,12 @@
         <v>0.9429999999999999</v>
       </c>
       <c r="F42" t="n">
+        <v>2.0062</v>
+      </c>
+      <c r="G42" t="n">
         <v>0.3848</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>0.6495</v>
       </c>
     </row>
@@ -1665,9 +1793,12 @@
         <v>0.9782999999999999</v>
       </c>
       <c r="F43" t="n">
+        <v>1.9929</v>
+      </c>
+      <c r="G43" t="n">
         <v>0.2867</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>0.6452</v>
       </c>
     </row>
@@ -1694,9 +1825,12 @@
         <v>0.9792</v>
       </c>
       <c r="F44" t="n">
+        <v>1.9981</v>
+      </c>
+      <c r="G44" t="n">
         <v>0.2526</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>0.6468</v>
       </c>
     </row>
@@ -1723,9 +1857,12 @@
         <v>0.9294</v>
       </c>
       <c r="F45" t="n">
+        <v>1.9943</v>
+      </c>
+      <c r="G45" t="n">
         <v>0.3947</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>0.6456</v>
       </c>
     </row>
@@ -1752,9 +1889,12 @@
         <v>0.9568</v>
       </c>
       <c r="F46" t="n">
+        <v>2.0216</v>
+      </c>
+      <c r="G46" t="n">
         <v>0.3493</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>0.6544</v>
       </c>
     </row>
@@ -1781,9 +1921,12 @@
         <v>0.9247</v>
       </c>
       <c r="F47" t="n">
+        <v>2.0356</v>
+      </c>
+      <c r="G47" t="n">
         <v>0.3989</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>0.6589</v>
       </c>
     </row>
@@ -1810,9 +1953,12 @@
         <v>0.972</v>
       </c>
       <c r="F48" t="n">
+        <v>1.9932</v>
+      </c>
+      <c r="G48" t="n">
         <v>0.312</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>0.6453</v>
       </c>
     </row>
@@ -1839,9 +1985,12 @@
         <v>0.9437</v>
       </c>
       <c r="F49" t="n">
+        <v>1.9986</v>
+      </c>
+      <c r="G49" t="n">
         <v>0.3859</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>0.647</v>
       </c>
     </row>
@@ -1868,9 +2017,12 @@
         <v>0.9019</v>
       </c>
       <c r="F50" t="n">
+        <v>2.007</v>
+      </c>
+      <c r="G50" t="n">
         <v>0.3996</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>0.6497000000000001</v>
       </c>
     </row>
@@ -1897,9 +2049,12 @@
         <v>0.8663</v>
       </c>
       <c r="F51" t="n">
+        <v>2.0808</v>
+      </c>
+      <c r="G51" t="n">
         <v>0.4268</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>0.6731</v>
       </c>
     </row>
@@ -1926,9 +2081,12 @@
         <v>0.8688</v>
       </c>
       <c r="F52" t="n">
+        <v>2.0965</v>
+      </c>
+      <c r="G52" t="n">
         <v>0.4278</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>0.678</v>
       </c>
     </row>
@@ -1955,9 +2113,12 @@
         <v>0.9121</v>
       </c>
       <c r="F53" t="n">
+        <v>2.0271</v>
+      </c>
+      <c r="G53" t="n">
         <v>0.3777</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>0.6562</v>
       </c>
     </row>
@@ -1984,9 +2145,12 @@
         <v>0.9085</v>
       </c>
       <c r="F54" t="n">
+        <v>2.0645</v>
+      </c>
+      <c r="G54" t="n">
         <v>0.3913</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>0.668</v>
       </c>
     </row>
@@ -2013,9 +2177,12 @@
         <v>0.9329</v>
       </c>
       <c r="F55" t="n">
+        <v>1.9873</v>
+      </c>
+      <c r="G55" t="n">
         <v>0.3451</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>0.6433</v>
       </c>
     </row>
@@ -2042,9 +2209,12 @@
         <v>0.9307</v>
       </c>
       <c r="F56" t="n">
+        <v>1.9703</v>
+      </c>
+      <c r="G56" t="n">
         <v>0.3622</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>0.6378</v>
       </c>
     </row>
@@ -2071,9 +2241,12 @@
         <v>0.9589</v>
       </c>
       <c r="F57" t="n">
+        <v>2.0044</v>
+      </c>
+      <c r="G57" t="n">
         <v>0.2948</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>0.6489</v>
       </c>
     </row>
@@ -2100,9 +2273,12 @@
         <v>0.8183</v>
       </c>
       <c r="F58" t="n">
+        <v>2.1307</v>
+      </c>
+      <c r="G58" t="n">
         <v>0.4422</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>0.6885</v>
       </c>
     </row>
@@ -2129,9 +2305,12 @@
         <v>0.8193</v>
       </c>
       <c r="F59" t="n">
+        <v>2.134</v>
+      </c>
+      <c r="G59" t="n">
         <v>0.4423</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>0.6895</v>
       </c>
     </row>
@@ -2158,9 +2337,12 @@
         <v>0.8174</v>
       </c>
       <c r="F60" t="n">
+        <v>2.1358</v>
+      </c>
+      <c r="G60" t="n">
         <v>0.4427</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>0.6899999999999999</v>
       </c>
     </row>
@@ -2187,9 +2369,12 @@
         <v>0.8928</v>
       </c>
       <c r="F61" t="n">
+        <v>2.1346</v>
+      </c>
+      <c r="G61" t="n">
         <v>0.3816</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>0.6897</v>
       </c>
     </row>
@@ -2216,9 +2401,12 @@
         <v>0.9191</v>
       </c>
       <c r="F62" t="n">
+        <v>2.0293</v>
+      </c>
+      <c r="G62" t="n">
         <v>0.3428</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>0.6569</v>
       </c>
     </row>
@@ -2245,9 +2433,12 @@
         <v>0.9097</v>
       </c>
       <c r="F63" t="n">
+        <v>2.0245</v>
+      </c>
+      <c r="G63" t="n">
         <v>0.3619</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>0.6553</v>
       </c>
     </row>
@@ -2274,9 +2465,12 @@
         <v>0.8593</v>
       </c>
       <c r="F64" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G64" t="n">
         <v>0.4101</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>0.6539</v>
       </c>
     </row>
@@ -2303,9 +2497,12 @@
         <v>0.9048</v>
       </c>
       <c r="F65" t="n">
+        <v>2.0301</v>
+      </c>
+      <c r="G65" t="n">
         <v>0.3665</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>0.6572</v>
       </c>
     </row>
@@ -2332,9 +2529,12 @@
         <v>0.9455</v>
       </c>
       <c r="F66" t="n">
+        <v>2.0066</v>
+      </c>
+      <c r="G66" t="n">
         <v>0.3278</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>0.6496</v>
       </c>
     </row>
@@ -2361,9 +2561,12 @@
         <v>0.9065</v>
       </c>
       <c r="F67" t="n">
+        <v>1.995</v>
+      </c>
+      <c r="G67" t="n">
         <v>0.3937</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>0.6459</v>
       </c>
     </row>
@@ -2390,9 +2593,12 @@
         <v>0.944</v>
       </c>
       <c r="F68" t="n">
+        <v>2.0025</v>
+      </c>
+      <c r="G68" t="n">
         <v>0.3265</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>0.6483</v>
       </c>
     </row>
@@ -2419,9 +2625,12 @@
         <v>0.9435</v>
       </c>
       <c r="F69" t="n">
+        <v>2.0559</v>
+      </c>
+      <c r="G69" t="n">
         <v>0.341</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>0.6653</v>
       </c>
     </row>
@@ -2448,9 +2657,12 @@
         <v>0.9414</v>
       </c>
       <c r="F70" t="n">
+        <v>2.0532</v>
+      </c>
+      <c r="G70" t="n">
         <v>0.3393</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>0.6645</v>
       </c>
     </row>
@@ -2477,9 +2689,12 @@
         <v>0.9319</v>
       </c>
       <c r="F71" t="n">
+        <v>2.0197</v>
+      </c>
+      <c r="G71" t="n">
         <v>0.3795</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>0.6538</v>
       </c>
     </row>
@@ -2506,9 +2721,12 @@
         <v>0.9292</v>
       </c>
       <c r="F72" t="n">
+        <v>2.0508</v>
+      </c>
+      <c r="G72" t="n">
         <v>0.3686</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>0.6637</v>
       </c>
     </row>
@@ -2535,9 +2753,12 @@
         <v>0.9436</v>
       </c>
       <c r="F73" t="n">
+        <v>2.0231</v>
+      </c>
+      <c r="G73" t="n">
         <v>0.385</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>0.6549</v>
       </c>
     </row>
@@ -2564,9 +2785,12 @@
         <v>0.9257</v>
       </c>
       <c r="F74" t="n">
+        <v>2.0623</v>
+      </c>
+      <c r="G74" t="n">
         <v>0.4141</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>0.6673</v>
       </c>
     </row>
@@ -2593,9 +2817,12 @@
         <v>0.9183</v>
       </c>
       <c r="F75" t="n">
+        <v>2.1139</v>
+      </c>
+      <c r="G75" t="n">
         <v>0.372</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>0.6833</v>
       </c>
     </row>
@@ -2622,9 +2849,12 @@
         <v>0.9183</v>
       </c>
       <c r="F76" t="n">
+        <v>2.1139</v>
+      </c>
+      <c r="G76" t="n">
         <v>0.372</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>0.6833</v>
       </c>
     </row>
@@ -2651,9 +2881,12 @@
         <v>0.8977000000000001</v>
       </c>
       <c r="F77" t="n">
+        <v>2.1095</v>
+      </c>
+      <c r="G77" t="n">
         <v>0.3732</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>0.6820000000000001</v>
       </c>
     </row>
@@ -2680,9 +2913,12 @@
         <v>0.8993</v>
       </c>
       <c r="F78" t="n">
+        <v>2.1084</v>
+      </c>
+      <c r="G78" t="n">
         <v>0.3727</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>0.6817</v>
       </c>
     </row>
@@ -2709,9 +2945,12 @@
         <v>0.8994</v>
       </c>
       <c r="F79" t="n">
+        <v>2.1088</v>
+      </c>
+      <c r="G79" t="n">
         <v>0.3718</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>0.6818</v>
       </c>
     </row>
@@ -2738,9 +2977,12 @@
         <v>0.8991</v>
       </c>
       <c r="F80" t="n">
+        <v>2.108</v>
+      </c>
+      <c r="G80" t="n">
         <v>0.3729</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>0.6815</v>
       </c>
     </row>
@@ -2767,9 +3009,12 @@
         <v>0.8689</v>
       </c>
       <c r="F81" t="n">
+        <v>2.0371</v>
+      </c>
+      <c r="G81" t="n">
         <v>0.4105</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>0.6594</v>
       </c>
     </row>
@@ -2796,9 +3041,12 @@
         <v>0.8648</v>
       </c>
       <c r="F82" t="n">
+        <v>2.0399</v>
+      </c>
+      <c r="G82" t="n">
         <v>0.4119</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>0.6603</v>
       </c>
     </row>
@@ -2825,9 +3073,12 @@
         <v>0.9152</v>
       </c>
       <c r="F83" t="n">
+        <v>2.1197</v>
+      </c>
+      <c r="G83" t="n">
         <v>0.3729</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>0.6851</v>
       </c>
     </row>
@@ -2854,9 +3105,12 @@
         <v>0.9320000000000001</v>
       </c>
       <c r="F84" t="n">
+        <v>2.1162</v>
+      </c>
+      <c r="G84" t="n">
         <v>0.3561</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>0.6840000000000001</v>
       </c>
     </row>
@@ -2883,9 +3137,12 @@
         <v>0.9324</v>
       </c>
       <c r="F85" t="n">
+        <v>2.121</v>
+      </c>
+      <c r="G85" t="n">
         <v>0.3535</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>0.6855</v>
       </c>
     </row>
@@ -2912,9 +3169,12 @@
         <v>0.9762</v>
       </c>
       <c r="F86" t="n">
+        <v>2.0353</v>
+      </c>
+      <c r="G86" t="n">
         <v>0.2931</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>0.6588000000000001</v>
       </c>
     </row>
@@ -2941,9 +3201,12 @@
         <v>0.9593</v>
       </c>
       <c r="F87" t="n">
+        <v>2.0435</v>
+      </c>
+      <c r="G87" t="n">
         <v>0.3502</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>0.6614</v>
       </c>
     </row>
@@ -2970,9 +3233,12 @@
         <v>0.9555</v>
       </c>
       <c r="F88" t="n">
+        <v>2.0236</v>
+      </c>
+      <c r="G88" t="n">
         <v>0.3349</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>0.6551</v>
       </c>
     </row>
@@ -2999,9 +3265,12 @@
         <v>0.9493</v>
       </c>
       <c r="F89" t="n">
+        <v>2.0311</v>
+      </c>
+      <c r="G89" t="n">
         <v>0.3347</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>0.6575</v>
       </c>
     </row>
@@ -3028,9 +3297,12 @@
         <v>0.9492</v>
       </c>
       <c r="F90" t="n">
+        <v>1.9932</v>
+      </c>
+      <c r="G90" t="n">
         <v>0.3693</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>0.6453</v>
       </c>
     </row>
@@ -3057,9 +3329,12 @@
         <v>0.9792</v>
       </c>
       <c r="F91" t="n">
+        <v>1.9967</v>
+      </c>
+      <c r="G91" t="n">
         <v>0.2526</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>0.6464</v>
       </c>
     </row>
@@ -3086,9 +3361,12 @@
         <v>0.9555</v>
       </c>
       <c r="F92" t="n">
+        <v>2.0236</v>
+      </c>
+      <c r="G92" t="n">
         <v>0.3349</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>0.6551</v>
       </c>
     </row>
@@ -3115,9 +3393,12 @@
         <v>0.9792</v>
       </c>
       <c r="F93" t="n">
+        <v>1.9967</v>
+      </c>
+      <c r="G93" t="n">
         <v>0.2526</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>0.6464</v>
       </c>
     </row>
@@ -3144,9 +3425,12 @@
         <v>0.8977000000000001</v>
       </c>
       <c r="F94" t="n">
+        <v>1.8785</v>
+      </c>
+      <c r="G94" t="n">
         <v>0.3401</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>0.6069</v>
       </c>
     </row>
@@ -3173,9 +3457,12 @@
         <v>0.7641</v>
       </c>
       <c r="F95" t="n">
+        <v>2.0074</v>
+      </c>
+      <c r="G95" t="n">
         <v>0.4542</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>0.6499</v>
       </c>
     </row>
@@ -3202,9 +3489,12 @@
         <v>0.8998</v>
       </c>
       <c r="F96" t="n">
+        <v>1.8959</v>
+      </c>
+      <c r="G96" t="n">
         <v>0.3309</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>0.6128</v>
       </c>
     </row>
@@ -3231,9 +3521,12 @@
         <v>0.8914</v>
       </c>
       <c r="F97" t="n">
+        <v>1.8873</v>
+      </c>
+      <c r="G97" t="n">
         <v>0.3457</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>0.6099</v>
       </c>
     </row>
@@ -3260,9 +3553,12 @@
         <v>0.9341</v>
       </c>
       <c r="F98" t="n">
+        <v>1.8507</v>
+      </c>
+      <c r="G98" t="n">
         <v>0.3053</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>0.5972</v>
       </c>
     </row>
@@ -3289,9 +3585,12 @@
         <v>0.9254</v>
       </c>
       <c r="F99" t="n">
+        <v>1.8416</v>
+      </c>
+      <c r="G99" t="n">
         <v>0.3071</v>
       </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>0.594</v>
       </c>
     </row>
@@ -3318,9 +3617,12 @@
         <v>0.9293</v>
       </c>
       <c r="F100" t="n">
+        <v>1.8635</v>
+      </c>
+      <c r="G100" t="n">
         <v>0.2993</v>
       </c>
-      <c r="G100" t="n">
+      <c r="H100" t="n">
         <v>0.6016</v>
       </c>
     </row>
@@ -3347,9 +3649,12 @@
         <v>0.9154</v>
       </c>
       <c r="F101" t="n">
+        <v>1.8741</v>
+      </c>
+      <c r="G101" t="n">
         <v>0.3207</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>0.6052999999999999</v>
       </c>
     </row>
@@ -3376,9 +3681,12 @@
         <v>0.9053</v>
       </c>
       <c r="F102" t="n">
+        <v>1.8772</v>
+      </c>
+      <c r="G102" t="n">
         <v>0.3387</v>
       </c>
-      <c r="G102" t="n">
+      <c r="H102" t="n">
         <v>0.6064000000000001</v>
       </c>
     </row>
@@ -3405,9 +3713,12 @@
         <v>0.9201</v>
       </c>
       <c r="F103" t="n">
+        <v>1.8619</v>
+      </c>
+      <c r="G103" t="n">
         <v>0.3392</v>
       </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>0.6011</v>
       </c>
     </row>
@@ -3434,9 +3745,12 @@
         <v>0.9443</v>
       </c>
       <c r="F104" t="n">
+        <v>1.8381</v>
+      </c>
+      <c r="G104" t="n">
         <v>0.2863</v>
       </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>0.5928</v>
       </c>
     </row>
@@ -3463,9 +3777,12 @@
         <v>0.9592000000000001</v>
       </c>
       <c r="F105" t="n">
+        <v>1.8466</v>
+      </c>
+      <c r="G105" t="n">
         <v>0.2559</v>
       </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>0.5957</v>
       </c>
     </row>
@@ -3492,9 +3809,12 @@
         <v>0.9333</v>
       </c>
       <c r="F106" t="n">
+        <v>1.8315</v>
+      </c>
+      <c r="G106" t="n">
         <v>0.2965</v>
       </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>0.5904</v>
       </c>
     </row>
@@ -3521,9 +3841,12 @@
         <v>0.9264</v>
       </c>
       <c r="F107" t="n">
+        <v>1.8762</v>
+      </c>
+      <c r="G107" t="n">
         <v>0.3052</v>
       </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>0.6061</v>
       </c>
     </row>
@@ -3550,9 +3873,12 @@
         <v>0.9369</v>
       </c>
       <c r="F108" t="n">
+        <v>1.8961</v>
+      </c>
+      <c r="G108" t="n">
         <v>0.3217</v>
       </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>0.6129</v>
       </c>
     </row>
@@ -3579,9 +3905,12 @@
         <v>0.9727</v>
       </c>
       <c r="F109" t="n">
+        <v>1.8934</v>
+      </c>
+      <c r="G109" t="n">
         <v>0.2378</v>
       </c>
-      <c r="G109" t="n">
+      <c r="H109" t="n">
         <v>0.612</v>
       </c>
     </row>
@@ -3608,9 +3937,12 @@
         <v>0.9548</v>
       </c>
       <c r="F110" t="n">
+        <v>1.8498</v>
+      </c>
+      <c r="G110" t="n">
         <v>0.2592</v>
       </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>0.5969</v>
       </c>
     </row>
@@ -3637,9 +3969,12 @@
         <v>0.9282</v>
       </c>
       <c r="F111" t="n">
+        <v>1.8314</v>
+      </c>
+      <c r="G111" t="n">
         <v>0.3072</v>
       </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>0.5904</v>
       </c>
     </row>
@@ -3666,9 +4001,12 @@
         <v>0.8921</v>
       </c>
       <c r="F112" t="n">
+        <v>1.8981</v>
+      </c>
+      <c r="G112" t="n">
         <v>0.3779</v>
       </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>0.6136</v>
       </c>
     </row>
@@ -3695,9 +4033,12 @@
         <v>0.9559</v>
       </c>
       <c r="F113" t="n">
+        <v>1.8883</v>
+      </c>
+      <c r="G113" t="n">
         <v>0.2797</v>
       </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>0.6102</v>
       </c>
     </row>
@@ -3724,9 +4065,12 @@
         <v>0.9267</v>
       </c>
       <c r="F114" t="n">
+        <v>1.8536</v>
+      </c>
+      <c r="G114" t="n">
         <v>0.3107</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>0.5982</v>
       </c>
     </row>
@@ -3753,9 +4097,12 @@
         <v>0.927</v>
       </c>
       <c r="F115" t="n">
+        <v>1.8302</v>
+      </c>
+      <c r="G115" t="n">
         <v>0.3073</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>0.5899</v>
       </c>
     </row>
@@ -3782,9 +4129,12 @@
         <v>0.9012</v>
       </c>
       <c r="F116" t="n">
+        <v>1.8922</v>
+      </c>
+      <c r="G116" t="n">
         <v>0.3443</v>
       </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>0.6116</v>
       </c>
     </row>
@@ -3811,9 +4161,12 @@
         <v>0.8463000000000001</v>
       </c>
       <c r="F117" t="n">
+        <v>1.8925</v>
+      </c>
+      <c r="G117" t="n">
         <v>0.3982</v>
       </c>
-      <c r="G117" t="n">
+      <c r="H117" t="n">
         <v>0.6117</v>
       </c>
     </row>
@@ -3840,9 +4193,12 @@
         <v>0.9592000000000001</v>
       </c>
       <c r="F118" t="n">
+        <v>1.8466</v>
+      </c>
+      <c r="G118" t="n">
         <v>0.2559</v>
       </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>0.5957</v>
       </c>
     </row>
@@ -3869,9 +4225,12 @@
         <v>0.9559</v>
       </c>
       <c r="F119" t="n">
+        <v>1.8883</v>
+      </c>
+      <c r="G119" t="n">
         <v>0.2797</v>
       </c>
-      <c r="G119" t="n">
+      <c r="H119" t="n">
         <v>0.6102</v>
       </c>
     </row>
@@ -3898,9 +4257,12 @@
         <v>0.8717</v>
       </c>
       <c r="F120" t="n">
+        <v>1.9518</v>
+      </c>
+      <c r="G120" t="n">
         <v>0.3661</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>0.6317</v>
       </c>
     </row>
@@ -3927,9 +4289,12 @@
         <v>0.8717</v>
       </c>
       <c r="F121" t="n">
+        <v>1.9518</v>
+      </c>
+      <c r="G121" t="n">
         <v>0.3661</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>0.6317</v>
       </c>
     </row>
@@ -3956,9 +4321,12 @@
         <v>0.9226</v>
       </c>
       <c r="F122" t="n">
+        <v>1.8631</v>
+      </c>
+      <c r="G122" t="n">
         <v>0.3141</v>
       </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>0.6015</v>
       </c>
     </row>
@@ -3985,9 +4353,12 @@
         <v>0.9558</v>
       </c>
       <c r="F123" t="n">
+        <v>1.8885</v>
+      </c>
+      <c r="G123" t="n">
         <v>0.2797</v>
       </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>0.6103</v>
       </c>
     </row>
@@ -4014,9 +4385,12 @@
         <v>0.9115</v>
       </c>
       <c r="F124" t="n">
+        <v>1.8598</v>
+      </c>
+      <c r="G124" t="n">
         <v>0.3414</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>0.6004</v>
       </c>
     </row>
@@ -4043,9 +4417,12 @@
         <v>0.9036999999999999</v>
       </c>
       <c r="F125" t="n">
+        <v>1.8778</v>
+      </c>
+      <c r="G125" t="n">
         <v>0.3264</v>
       </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>0.6066</v>
       </c>
     </row>
@@ -4072,9 +4449,12 @@
         <v>0.9536</v>
       </c>
       <c r="F126" t="n">
+        <v>1.9328</v>
+      </c>
+      <c r="G126" t="n">
         <v>0.2837</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>0.6254</v>
       </c>
     </row>
@@ -4101,9 +4481,12 @@
         <v>0.8697</v>
       </c>
       <c r="F127" t="n">
+        <v>2.025</v>
+      </c>
+      <c r="G127" t="n">
         <v>0.394</v>
       </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>0.6555</v>
       </c>
     </row>
@@ -4130,9 +4513,12 @@
         <v>0.9115</v>
       </c>
       <c r="F128" t="n">
+        <v>1.9495</v>
+      </c>
+      <c r="G128" t="n">
         <v>0.3506</v>
       </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>0.6309</v>
       </c>
     </row>
@@ -4159,9 +4545,12 @@
         <v>0.9719</v>
       </c>
       <c r="F129" t="n">
+        <v>1.9531</v>
+      </c>
+      <c r="G129" t="n">
         <v>0.2391</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>0.6321</v>
       </c>
     </row>
@@ -4188,9 +4577,12 @@
         <v>0.9717</v>
       </c>
       <c r="F130" t="n">
+        <v>1.9424</v>
+      </c>
+      <c r="G130" t="n">
         <v>0.2391</v>
       </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>0.6284999999999999</v>
       </c>
     </row>
@@ -4217,9 +4609,12 @@
         <v>0.9719</v>
       </c>
       <c r="F131" t="n">
+        <v>1.9327</v>
+      </c>
+      <c r="G131" t="n">
         <v>0.2389</v>
       </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>0.6253</v>
       </c>
     </row>
@@ -4246,9 +4641,12 @@
         <v>0.973</v>
       </c>
       <c r="F132" t="n">
+        <v>1.9575</v>
+      </c>
+      <c r="G132" t="n">
         <v>0.2408</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>0.6336000000000001</v>
       </c>
     </row>
@@ -4275,9 +4673,12 @@
         <v>0.9216</v>
       </c>
       <c r="F133" t="n">
+        <v>1.9483</v>
+      </c>
+      <c r="G133" t="n">
         <v>0.3325</v>
       </c>
-      <c r="G133" t="n">
+      <c r="H133" t="n">
         <v>0.6304999999999999</v>
       </c>
     </row>
@@ -4297,16 +4698,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.9112</v>
+        <v>0.9111</v>
       </c>
       <c r="F134" t="n">
-        <v>0.3505</v>
+        <v>1.9516</v>
       </c>
       <c r="G134" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="H134" t="n">
         <v>0.6316000000000001</v>
       </c>
     </row>
@@ -4333,9 +4737,12 @@
         <v>0.9185</v>
       </c>
       <c r="F135" t="n">
+        <v>1.9435</v>
+      </c>
+      <c r="G135" t="n">
         <v>0.3332</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>0.6289</v>
       </c>
     </row>
@@ -4362,9 +4769,12 @@
         <v>0.9214</v>
       </c>
       <c r="F136" t="n">
+        <v>1.9351</v>
+      </c>
+      <c r="G136" t="n">
         <v>0.3346</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>0.6261</v>
       </c>
     </row>
@@ -4391,9 +4801,12 @@
         <v>0.975</v>
       </c>
       <c r="F137" t="n">
+        <v>1.9708</v>
+      </c>
+      <c r="G137" t="n">
         <v>0.2426</v>
       </c>
-      <c r="G137" t="n">
+      <c r="H137" t="n">
         <v>0.6379</v>
       </c>
     </row>
@@ -4420,9 +4833,12 @@
         <v>0.9798</v>
       </c>
       <c r="F138" t="n">
+        <v>1.9795</v>
+      </c>
+      <c r="G138" t="n">
         <v>0.2421</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>0.6408</v>
       </c>
     </row>
@@ -4449,9 +4865,12 @@
         <v>0.9658</v>
       </c>
       <c r="F139" t="n">
+        <v>1.9551</v>
+      </c>
+      <c r="G139" t="n">
         <v>0.2738</v>
       </c>
-      <c r="G139" t="n">
+      <c r="H139" t="n">
         <v>0.6328</v>
       </c>
     </row>
@@ -4478,9 +4897,12 @@
         <v>0.98</v>
       </c>
       <c r="F140" t="n">
+        <v>2.0091</v>
+      </c>
+      <c r="G140" t="n">
         <v>0.283</v>
       </c>
-      <c r="G140" t="n">
+      <c r="H140" t="n">
         <v>0.6504</v>
       </c>
     </row>
@@ -4507,9 +4929,12 @@
         <v>0.9326</v>
       </c>
       <c r="F141" t="n">
+        <v>2.0022</v>
+      </c>
+      <c r="G141" t="n">
         <v>0.3972</v>
       </c>
-      <c r="G141" t="n">
+      <c r="H141" t="n">
         <v>0.6482</v>
       </c>
     </row>
@@ -4536,9 +4961,12 @@
         <v>0.9798</v>
       </c>
       <c r="F142" t="n">
+        <v>1.9795</v>
+      </c>
+      <c r="G142" t="n">
         <v>0.2421</v>
       </c>
-      <c r="G142" t="n">
+      <c r="H142" t="n">
         <v>0.6408</v>
       </c>
     </row>
@@ -4565,9 +4993,12 @@
         <v>0.9465</v>
       </c>
       <c r="F143" t="n">
+        <v>1.9985</v>
+      </c>
+      <c r="G143" t="n">
         <v>0.3112</v>
       </c>
-      <c r="G143" t="n">
+      <c r="H143" t="n">
         <v>0.647</v>
       </c>
     </row>
@@ -4594,9 +5025,12 @@
         <v>0.9442</v>
       </c>
       <c r="F144" t="n">
+        <v>1.9674</v>
+      </c>
+      <c r="G144" t="n">
         <v>0.3097</v>
       </c>
-      <c r="G144" t="n">
+      <c r="H144" t="n">
         <v>0.6368</v>
       </c>
     </row>
@@ -4623,9 +5057,12 @@
         <v>0.9326</v>
       </c>
       <c r="F145" t="n">
+        <v>2.0022</v>
+      </c>
+      <c r="G145" t="n">
         <v>0.3972</v>
       </c>
-      <c r="G145" t="n">
+      <c r="H145" t="n">
         <v>0.6482</v>
       </c>
     </row>
@@ -4652,9 +5089,12 @@
         <v>0.8701</v>
       </c>
       <c r="F146" t="n">
+        <v>2.0198</v>
+      </c>
+      <c r="G146" t="n">
         <v>0.3943</v>
       </c>
-      <c r="G146" t="n">
+      <c r="H146" t="n">
         <v>0.6539</v>
       </c>
     </row>
@@ -4681,9 +5121,12 @@
         <v>0.8673999999999999</v>
       </c>
       <c r="F147" t="n">
+        <v>2.0187</v>
+      </c>
+      <c r="G147" t="n">
         <v>0.3963</v>
       </c>
-      <c r="G147" t="n">
+      <c r="H147" t="n">
         <v>0.6535</v>
       </c>
     </row>
@@ -4710,9 +5153,12 @@
         <v>0.8659</v>
       </c>
       <c r="F148" t="n">
+        <v>2.0183</v>
+      </c>
+      <c r="G148" t="n">
         <v>0.3974</v>
       </c>
-      <c r="G148" t="n">
+      <c r="H148" t="n">
         <v>0.6534</v>
       </c>
     </row>
@@ -4739,9 +5185,12 @@
         <v>0.8677</v>
       </c>
       <c r="F149" t="n">
+        <v>2.0106</v>
+      </c>
+      <c r="G149" t="n">
         <v>0.3942</v>
       </c>
-      <c r="G149" t="n">
+      <c r="H149" t="n">
         <v>0.6509</v>
       </c>
     </row>
@@ -4768,9 +5217,12 @@
         <v>0.8691</v>
       </c>
       <c r="F150" t="n">
+        <v>2.0286</v>
+      </c>
+      <c r="G150" t="n">
         <v>0.3939</v>
       </c>
-      <c r="G150" t="n">
+      <c r="H150" t="n">
         <v>0.6567</v>
       </c>
     </row>
@@ -4790,16 +5242,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.8687</v>
+        <v>0.8685</v>
       </c>
       <c r="F151" t="n">
-        <v>0.3942</v>
+        <v>2.0272</v>
       </c>
       <c r="G151" t="n">
+        <v>0.3944</v>
+      </c>
+      <c r="H151" t="n">
         <v>0.6562</v>
       </c>
     </row>
@@ -4826,9 +5281,12 @@
         <v>0.8692</v>
       </c>
       <c r="F152" t="n">
+        <v>2.0244</v>
+      </c>
+      <c r="G152" t="n">
         <v>0.3944</v>
       </c>
-      <c r="G152" t="n">
+      <c r="H152" t="n">
         <v>0.6553</v>
       </c>
     </row>
@@ -4855,9 +5313,12 @@
         <v>0.8688</v>
       </c>
       <c r="F153" t="n">
+        <v>2.0214</v>
+      </c>
+      <c r="G153" t="n">
         <v>0.3942</v>
       </c>
-      <c r="G153" t="n">
+      <c r="H153" t="n">
         <v>0.6544</v>
       </c>
     </row>
@@ -4884,9 +5345,12 @@
         <v>0.8683999999999999</v>
       </c>
       <c r="F154" t="n">
+        <v>2.0219</v>
+      </c>
+      <c r="G154" t="n">
         <v>0.3945</v>
       </c>
-      <c r="G154" t="n">
+      <c r="H154" t="n">
         <v>0.6545</v>
       </c>
     </row>
@@ -4913,9 +5377,12 @@
         <v>0.8927</v>
       </c>
       <c r="F155" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="G155" t="n">
         <v>0.384</v>
       </c>
-      <c r="G155" t="n">
+      <c r="H155" t="n">
         <v>0.6571</v>
       </c>
     </row>
@@ -4942,9 +5409,12 @@
         <v>0.896</v>
       </c>
       <c r="F156" t="n">
+        <v>2.0363</v>
+      </c>
+      <c r="G156" t="n">
         <v>0.3781</v>
       </c>
-      <c r="G156" t="n">
+      <c r="H156" t="n">
         <v>0.6591</v>
       </c>
     </row>
@@ -4971,9 +5441,12 @@
         <v>0.9527</v>
       </c>
       <c r="F157" t="n">
+        <v>2.0325</v>
+      </c>
+      <c r="G157" t="n">
         <v>0.2993</v>
       </c>
-      <c r="G157" t="n">
+      <c r="H157" t="n">
         <v>0.6579</v>
       </c>
     </row>
@@ -5000,9 +5473,12 @@
         <v>0.9245</v>
       </c>
       <c r="F158" t="n">
+        <v>1.9721</v>
+      </c>
+      <c r="G158" t="n">
         <v>0.3585</v>
       </c>
-      <c r="G158" t="n">
+      <c r="H158" t="n">
         <v>0.6384</v>
       </c>
     </row>
@@ -5029,9 +5505,12 @@
         <v>0.9721</v>
       </c>
       <c r="F159" t="n">
+        <v>2.0018</v>
+      </c>
+      <c r="G159" t="n">
         <v>0.2489</v>
       </c>
-      <c r="G159" t="n">
+      <c r="H159" t="n">
         <v>0.6481</v>
       </c>
     </row>
@@ -5058,9 +5537,12 @@
         <v>0.9039</v>
       </c>
       <c r="F160" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="G160" t="n">
         <v>0.3621</v>
       </c>
-      <c r="G160" t="n">
+      <c r="H160" t="n">
         <v>0.6501</v>
       </c>
     </row>
@@ -5087,9 +5569,12 @@
         <v>0.9014</v>
       </c>
       <c r="F161" t="n">
+        <v>1.9991</v>
+      </c>
+      <c r="G161" t="n">
         <v>0.3629</v>
       </c>
-      <c r="G161" t="n">
+      <c r="H161" t="n">
         <v>0.6472</v>
       </c>
     </row>
@@ -5116,9 +5601,12 @@
         <v>0.896</v>
       </c>
       <c r="F162" t="n">
+        <v>2.0163</v>
+      </c>
+      <c r="G162" t="n">
         <v>0.3822</v>
       </c>
-      <c r="G162" t="n">
+      <c r="H162" t="n">
         <v>0.6526999999999999</v>
       </c>
     </row>
@@ -5145,9 +5633,12 @@
         <v>0.8914</v>
       </c>
       <c r="F163" t="n">
+        <v>2.0228</v>
+      </c>
+      <c r="G163" t="n">
         <v>0.4072</v>
       </c>
-      <c r="G163" t="n">
+      <c r="H163" t="n">
         <v>0.6548</v>
       </c>
     </row>
@@ -5174,9 +5665,12 @@
         <v>0.9802</v>
       </c>
       <c r="F164" t="n">
+        <v>2.0084</v>
+      </c>
+      <c r="G164" t="n">
         <v>0.2827</v>
       </c>
-      <c r="G164" t="n">
+      <c r="H164" t="n">
         <v>0.6502</v>
       </c>
     </row>
@@ -5203,9 +5697,12 @@
         <v>0.9036999999999999</v>
       </c>
       <c r="F165" t="n">
+        <v>1.8778</v>
+      </c>
+      <c r="G165" t="n">
         <v>0.3264</v>
       </c>
-      <c r="G165" t="n">
+      <c r="H165" t="n">
         <v>0.6066</v>
       </c>
     </row>
@@ -5232,9 +5729,12 @@
         <v>0.7635999999999999</v>
       </c>
       <c r="F166" t="n">
+        <v>2.0114</v>
+      </c>
+      <c r="G166" t="n">
         <v>0.4548</v>
       </c>
-      <c r="G166" t="n">
+      <c r="H166" t="n">
         <v>0.6511</v>
       </c>
     </row>
@@ -5261,9 +5761,12 @@
         <v>0.9574</v>
       </c>
       <c r="F167" t="n">
+        <v>1.9553</v>
+      </c>
+      <c r="G167" t="n">
         <v>0.3041</v>
       </c>
-      <c r="G167" t="n">
+      <c r="H167" t="n">
         <v>0.6328</v>
       </c>
     </row>
@@ -5290,9 +5793,12 @@
         <v>0.9503</v>
       </c>
       <c r="F168" t="n">
+        <v>1.9897</v>
+      </c>
+      <c r="G168" t="n">
         <v>0.3596</v>
       </c>
-      <c r="G168" t="n">
+      <c r="H168" t="n">
         <v>0.6441</v>
       </c>
     </row>
@@ -5319,9 +5825,12 @@
         <v>0.9671</v>
       </c>
       <c r="F169" t="n">
+        <v>1.9658</v>
+      </c>
+      <c r="G169" t="n">
         <v>0.2836</v>
       </c>
-      <c r="G169" t="n">
+      <c r="H169" t="n">
         <v>0.6363</v>
       </c>
     </row>
@@ -5348,9 +5857,12 @@
         <v>0.9473</v>
       </c>
       <c r="F170" t="n">
+        <v>2.0229</v>
+      </c>
+      <c r="G170" t="n">
         <v>0.3799</v>
       </c>
-      <c r="G170" t="n">
+      <c r="H170" t="n">
         <v>0.6548</v>
       </c>
     </row>
@@ -5377,9 +5889,12 @@
         <v>0.9393</v>
       </c>
       <c r="F171" t="n">
+        <v>1.9997</v>
+      </c>
+      <c r="G171" t="n">
         <v>0.3869</v>
       </c>
-      <c r="G171" t="n">
+      <c r="H171" t="n">
         <v>0.6474</v>
       </c>
     </row>
@@ -5406,9 +5921,12 @@
         <v>0.9771</v>
       </c>
       <c r="F172" t="n">
+        <v>2.0243</v>
+      </c>
+      <c r="G172" t="n">
         <v>0.2415</v>
       </c>
-      <c r="G172" t="n">
+      <c r="H172" t="n">
         <v>0.6553</v>
       </c>
     </row>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C18.1n7/RANDOMSEARCH_DETAILS_C18.1n7.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C18.1n7/RANDOMSEARCH_DETAILS_C18.1n7.xlsx
@@ -474,20 +474,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9347</v>
+        <v>0.9792</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9834</v>
+        <v>0.0625</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3655</v>
+        <v>0.2534</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6421</v>
+        <v>0.6364</v>
       </c>
     </row>
     <row r="3">
@@ -506,20 +506,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9686</v>
+        <v>0.9653</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9926</v>
+        <v>0.098</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3067</v>
+        <v>0.3075</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6451</v>
+        <v>0.6243</v>
       </c>
     </row>
     <row r="4">
@@ -538,20 +538,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.9403</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8785</v>
+        <v>0.241</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3401</v>
+        <v>0.2647</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6069</v>
+        <v>0.5726</v>
       </c>
     </row>
     <row r="5">
@@ -570,20 +570,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8998</v>
+        <v>0.8117</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1425</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3772</v>
+        <v>0.4477</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6921</v>
+        <v>0.6776</v>
       </c>
     </row>
     <row r="6">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8186</v>
+        <v>0.8096</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1309</v>
+        <v>-0.0677</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4415</v>
+        <v>0.4475</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6885</v>
+        <v>0.6792</v>
       </c>
     </row>
     <row r="7">
@@ -634,20 +634,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.919</v>
+        <v>0.9169</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0884</v>
+        <v>-0.0275</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3531</v>
+        <v>0.3614</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6755</v>
+        <v>0.6663</v>
       </c>
     </row>
     <row r="8">
@@ -670,16 +670,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9349</v>
+        <v>0.9237</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0429</v>
+        <v>-0.0707</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3493</v>
+        <v>0.3521</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6612</v>
+        <v>0.6801</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.974</v>
+        <v>0.9817</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9675</v>
+        <v>0.0537</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2779</v>
+        <v>0.2796</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6369</v>
+        <v>0.6394</v>
       </c>
     </row>
     <row r="10">
@@ -730,20 +730,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9392</v>
+        <v>0.9193</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0429</v>
+        <v>-0.059</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3332</v>
+        <v>0.3575</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6612</v>
+        <v>0.6764</v>
       </c>
     </row>
     <row r="11">
@@ -762,20 +762,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9277</v>
+        <v>0.9578</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0533</v>
+        <v>-0.064</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3526</v>
+        <v>0.2875</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6645</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="12">
@@ -794,20 +794,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9257</v>
+        <v>0.9584</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0653</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3544</v>
+        <v>0.2867</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6683</v>
+        <v>0.6802</v>
       </c>
     </row>
     <row r="13">
@@ -826,20 +826,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9537</v>
+        <v>0.9129</v>
       </c>
       <c r="F13" t="n">
-        <v>2.052</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3039</v>
+        <v>0.3708</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6641</v>
+        <v>0.6788999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -862,16 +862,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9286</v>
+        <v>0.9194</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0509</v>
+        <v>-0.0604</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3494</v>
+        <v>0.3568</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6637999999999999</v>
+        <v>0.6768999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -890,20 +890,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9553</v>
+        <v>0.9566</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0581</v>
+        <v>-0.0675</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3035</v>
+        <v>0.2881</v>
       </c>
       <c r="H15" t="n">
-        <v>0.666</v>
+        <v>0.6791</v>
       </c>
     </row>
     <row r="16">
@@ -922,20 +922,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.953</v>
+        <v>0.9179</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0559</v>
+        <v>-0.0716</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3049</v>
+        <v>0.3588</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6653</v>
+        <v>0.6804</v>
       </c>
     </row>
     <row r="17">
@@ -954,20 +954,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9235</v>
+        <v>0.9595</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0574</v>
+        <v>-0.0716</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3532</v>
+        <v>0.2864</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.6804</v>
       </c>
     </row>
     <row r="18">
@@ -986,20 +986,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9623</v>
+        <v>0.9689</v>
       </c>
       <c r="F18" t="n">
-        <v>1.988</v>
+        <v>0.0555</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3175</v>
+        <v>0.2958</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6435999999999999</v>
+        <v>0.6388</v>
       </c>
     </row>
     <row r="19">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.9748</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9993</v>
+        <v>0.031</v>
       </c>
       <c r="G19" t="n">
-        <v>0.326</v>
+        <v>0.2385</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6473</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="20">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9038</v>
+        <v>0.9245</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0544</v>
+        <v>0.0144</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4167</v>
+        <v>0.3793</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6525</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.9387</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0467</v>
+        <v>-0.0046</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3311</v>
+        <v>0.3634</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6624</v>
+        <v>0.6588000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1118,16 +1118,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9454</v>
+        <v>0.9444</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0441</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3311</v>
+        <v>0.3174</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6616</v>
+        <v>0.6546999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1146,20 +1146,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9452</v>
+        <v>0.9377</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0461</v>
+        <v>0.0052</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3378</v>
+        <v>0.3439</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6622</v>
+        <v>0.6556</v>
       </c>
     </row>
     <row r="24">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.8882</v>
+        <v>0.9403</v>
       </c>
       <c r="F24" t="n">
-        <v>2.0554</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>0.424</v>
+        <v>0.3435</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6652</v>
+        <v>0.6543</v>
       </c>
     </row>
     <row r="25">
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.8883</v>
+        <v>0.9332</v>
       </c>
       <c r="F25" t="n">
-        <v>2.0611</v>
+        <v>0.0049</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4212</v>
+        <v>0.3431</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6669</v>
+        <v>0.6556999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9755</v>
+        <v>0.9798</v>
       </c>
       <c r="F26" t="n">
-        <v>1.973</v>
+        <v>0.0599</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2883</v>
+        <v>0.2687</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6387</v>
+        <v>0.6373</v>
       </c>
     </row>
     <row r="27">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9619</v>
+        <v>0.9811</v>
       </c>
       <c r="F27" t="n">
-        <v>1.9881</v>
+        <v>0.058</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3136</v>
+        <v>0.2525</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6435999999999999</v>
+        <v>0.6379</v>
       </c>
     </row>
     <row r="28">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9459</v>
+        <v>0.9468</v>
       </c>
       <c r="F28" t="n">
-        <v>2.0103</v>
+        <v>0.0428</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3598</v>
+        <v>0.3513</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6508</v>
+        <v>0.6431</v>
       </c>
     </row>
     <row r="29">
@@ -1338,20 +1338,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9527</v>
+        <v>0.9429</v>
       </c>
       <c r="F29" t="n">
-        <v>2.0239</v>
+        <v>0.0222</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3261</v>
+        <v>0.3591</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6552</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="30">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9389</v>
+        <v>0.9159</v>
       </c>
       <c r="F30" t="n">
-        <v>2.0345</v>
+        <v>0.0098</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3675</v>
+        <v>0.4089</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6585</v>
+        <v>0.6541</v>
       </c>
     </row>
     <row r="31">
@@ -1402,20 +1402,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9542</v>
+        <v>0.9525</v>
       </c>
       <c r="F31" t="n">
-        <v>2.0503</v>
+        <v>0.0205</v>
       </c>
       <c r="G31" t="n">
-        <v>0.319</v>
+        <v>0.324</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6636</v>
+        <v>0.6505</v>
       </c>
     </row>
     <row r="32">
@@ -1434,20 +1434,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9016</v>
+        <v>0.9415</v>
       </c>
       <c r="F32" t="n">
-        <v>2.0505</v>
+        <v>0.0067</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4155</v>
+        <v>0.3408</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6636</v>
+        <v>0.6551</v>
       </c>
     </row>
     <row r="33">
@@ -1466,20 +1466,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9495</v>
+        <v>0.9473</v>
       </c>
       <c r="F33" t="n">
-        <v>2.0272</v>
+        <v>0.0114</v>
       </c>
       <c r="G33" t="n">
-        <v>0.329</v>
+        <v>0.3169</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6562</v>
+        <v>0.6535</v>
       </c>
     </row>
     <row r="34">
@@ -1498,20 +1498,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9487</v>
+        <v>0.9843</v>
       </c>
       <c r="F34" t="n">
-        <v>1.9792</v>
+        <v>0.0756</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3775</v>
+        <v>0.2493</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6407</v>
+        <v>0.632</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9437</v>
+        <v>0.968</v>
       </c>
       <c r="F35" t="n">
-        <v>2.0088</v>
+        <v>0.0381</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3851</v>
+        <v>0.3086</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6503</v>
+        <v>0.6447000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1562,20 +1562,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9678</v>
       </c>
       <c r="F36" t="n">
-        <v>1.9887</v>
+        <v>0.0673</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3322</v>
+        <v>0.3068</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6438</v>
+        <v>0.6348</v>
       </c>
     </row>
     <row r="37">
@@ -1594,20 +1594,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9361</v>
+        <v>0.9817</v>
       </c>
       <c r="F37" t="n">
-        <v>2.002</v>
+        <v>0.0328</v>
       </c>
       <c r="G37" t="n">
-        <v>0.3929</v>
+        <v>0.2369</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6481</v>
+        <v>0.6464</v>
       </c>
     </row>
     <row r="38">
@@ -1626,20 +1626,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.952</v>
+        <v>0.979</v>
       </c>
       <c r="F38" t="n">
-        <v>1.9814</v>
+        <v>0.045</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3457</v>
+        <v>0.2629</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6414</v>
+        <v>0.6423</v>
       </c>
     </row>
     <row r="39">
@@ -1658,20 +1658,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9398</v>
+        <v>0.9281</v>
       </c>
       <c r="F39" t="n">
-        <v>2.0049</v>
+        <v>0.0504</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3685</v>
+        <v>0.3697</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6491</v>
+        <v>0.6405</v>
       </c>
     </row>
     <row r="40">
@@ -1690,20 +1690,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9487</v>
+        <v>0.9533</v>
       </c>
       <c r="F40" t="n">
-        <v>2.0117</v>
+        <v>0.0161</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3628</v>
+        <v>0.3246</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6512</v>
+        <v>0.652</v>
       </c>
     </row>
     <row r="41">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9483</v>
+        <v>0.9756</v>
       </c>
       <c r="F41" t="n">
-        <v>1.9781</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3778</v>
+        <v>0.2869</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6403</v>
+        <v>0.6324</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9758</v>
       </c>
       <c r="F42" t="n">
-        <v>2.0062</v>
+        <v>0.04</v>
       </c>
       <c r="G42" t="n">
-        <v>0.3848</v>
+        <v>0.2652</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6495</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="43">
@@ -1786,20 +1786,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9679</v>
       </c>
       <c r="F43" t="n">
-        <v>1.9929</v>
+        <v>0.062</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2867</v>
+        <v>0.3073</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6452</v>
+        <v>0.6366000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -1822,16 +1822,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9792</v>
+        <v>0.9821</v>
       </c>
       <c r="F44" t="n">
-        <v>1.9981</v>
+        <v>0.0323</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2526</v>
+        <v>0.237</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6468</v>
+        <v>0.6466</v>
       </c>
     </row>
     <row r="45">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9294</v>
+        <v>0.9785</v>
       </c>
       <c r="F45" t="n">
-        <v>1.9943</v>
+        <v>0.0435</v>
       </c>
       <c r="G45" t="n">
-        <v>0.3947</v>
+        <v>0.2649</v>
       </c>
       <c r="H45" t="n">
-        <v>0.6456</v>
+        <v>0.6429</v>
       </c>
     </row>
     <row r="46">
@@ -1882,20 +1882,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9568</v>
+        <v>0.9389</v>
       </c>
       <c r="F46" t="n">
-        <v>2.0216</v>
+        <v>0.0186</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3493</v>
+        <v>0.3715</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6544</v>
+        <v>0.6512</v>
       </c>
     </row>
     <row r="47">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9247</v>
+        <v>0.9527</v>
       </c>
       <c r="F47" t="n">
-        <v>2.0356</v>
+        <v>0.0129</v>
       </c>
       <c r="G47" t="n">
-        <v>0.3989</v>
+        <v>0.3273</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6589</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="48">
@@ -1946,20 +1946,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.972</v>
+        <v>0.9673</v>
       </c>
       <c r="F48" t="n">
-        <v>1.9932</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>0.312</v>
+        <v>0.3067</v>
       </c>
       <c r="H48" t="n">
-        <v>0.6453</v>
+        <v>0.6309</v>
       </c>
     </row>
     <row r="49">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9437</v>
+        <v>0.9558</v>
       </c>
       <c r="F49" t="n">
-        <v>1.9986</v>
+        <v>0.0698</v>
       </c>
       <c r="G49" t="n">
-        <v>0.3859</v>
+        <v>0.3345</v>
       </c>
       <c r="H49" t="n">
-        <v>0.647</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="50">
@@ -2014,16 +2014,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9019</v>
+        <v>0.9016</v>
       </c>
       <c r="F50" t="n">
-        <v>2.007</v>
+        <v>0.0236</v>
       </c>
       <c r="G50" t="n">
-        <v>0.3996</v>
+        <v>0.3944</v>
       </c>
       <c r="H50" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.6495</v>
       </c>
     </row>
     <row r="51">
@@ -2042,20 +2042,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.8663</v>
+        <v>0.9001</v>
       </c>
       <c r="F51" t="n">
-        <v>2.0808</v>
+        <v>-0.0323</v>
       </c>
       <c r="G51" t="n">
-        <v>0.4268</v>
+        <v>0.3906</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6731</v>
+        <v>0.6677999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2074,20 +2074,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.8688</v>
+        <v>0.8978</v>
       </c>
       <c r="F52" t="n">
-        <v>2.0965</v>
+        <v>-0.0464</v>
       </c>
       <c r="G52" t="n">
-        <v>0.4278</v>
+        <v>0.3918</v>
       </c>
       <c r="H52" t="n">
-        <v>0.678</v>
+        <v>0.6724</v>
       </c>
     </row>
     <row r="53">
@@ -2106,20 +2106,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9121</v>
+        <v>0.9101</v>
       </c>
       <c r="F53" t="n">
-        <v>2.0271</v>
+        <v>-0.017</v>
       </c>
       <c r="G53" t="n">
-        <v>0.3777</v>
+        <v>0.3916</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6562</v>
+        <v>0.6629</v>
       </c>
     </row>
     <row r="54">
@@ -2138,20 +2138,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.9085</v>
+        <v>0.8724</v>
       </c>
       <c r="F54" t="n">
-        <v>2.0645</v>
+        <v>-0.0644</v>
       </c>
       <c r="G54" t="n">
-        <v>0.3913</v>
+        <v>0.4235</v>
       </c>
       <c r="H54" t="n">
-        <v>0.668</v>
+        <v>0.6781</v>
       </c>
     </row>
     <row r="55">
@@ -2170,20 +2170,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.9329</v>
+        <v>0.9181</v>
       </c>
       <c r="F55" t="n">
-        <v>1.9873</v>
+        <v>0.0694</v>
       </c>
       <c r="G55" t="n">
         <v>0.3451</v>
       </c>
       <c r="H55" t="n">
-        <v>0.6433</v>
+        <v>0.6341</v>
       </c>
     </row>
     <row r="56">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9307</v>
+        <v>0.9293</v>
       </c>
       <c r="F56" t="n">
-        <v>1.9703</v>
+        <v>0.1077</v>
       </c>
       <c r="G56" t="n">
-        <v>0.3622</v>
+        <v>0.3453</v>
       </c>
       <c r="H56" t="n">
-        <v>0.6378</v>
+        <v>0.6209</v>
       </c>
     </row>
     <row r="57">
@@ -2234,20 +2234,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9589</v>
+        <v>0.9715</v>
       </c>
       <c r="F57" t="n">
-        <v>2.0044</v>
+        <v>0.0667</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2948</v>
+        <v>0.2526</v>
       </c>
       <c r="H57" t="n">
-        <v>0.6489</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="58">
@@ -2270,16 +2270,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8183</v>
+        <v>0.8082</v>
       </c>
       <c r="F58" t="n">
-        <v>2.1307</v>
+        <v>-0.0692</v>
       </c>
       <c r="G58" t="n">
-        <v>0.4422</v>
+        <v>0.4479</v>
       </c>
       <c r="H58" t="n">
-        <v>0.6885</v>
+        <v>0.6797</v>
       </c>
     </row>
     <row r="59">
@@ -2302,16 +2302,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8193</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>2.134</v>
+        <v>-0.0716</v>
       </c>
       <c r="G59" t="n">
-        <v>0.4423</v>
+        <v>0.4485</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6895</v>
+        <v>0.6804</v>
       </c>
     </row>
     <row r="60">
@@ -2334,16 +2334,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.8174</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="F60" t="n">
-        <v>2.1358</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>0.4427</v>
+        <v>0.4487</v>
       </c>
       <c r="H60" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6808</v>
       </c>
     </row>
     <row r="61">
@@ -2362,20 +2362,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.8928</v>
+        <v>0.8067</v>
       </c>
       <c r="F61" t="n">
-        <v>2.1346</v>
+        <v>-0.0733</v>
       </c>
       <c r="G61" t="n">
-        <v>0.3816</v>
+        <v>0.4496</v>
       </c>
       <c r="H61" t="n">
-        <v>0.6897</v>
+        <v>0.681</v>
       </c>
     </row>
     <row r="62">
@@ -2394,20 +2394,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.9191</v>
+        <v>0.8572</v>
       </c>
       <c r="F62" t="n">
-        <v>2.0293</v>
+        <v>0.0203</v>
       </c>
       <c r="G62" t="n">
-        <v>0.3428</v>
+        <v>0.4119</v>
       </c>
       <c r="H62" t="n">
-        <v>0.6569</v>
+        <v>0.6506</v>
       </c>
     </row>
     <row r="63">
@@ -2426,20 +2426,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.9097</v>
+        <v>0.8958</v>
       </c>
       <c r="F63" t="n">
-        <v>2.0245</v>
+        <v>0.0272</v>
       </c>
       <c r="G63" t="n">
-        <v>0.3619</v>
+        <v>0.3706</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6553</v>
+        <v>0.6483</v>
       </c>
     </row>
     <row r="64">
@@ -2462,16 +2462,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8593</v>
+        <v>0.8532</v>
       </c>
       <c r="F64" t="n">
-        <v>2.02</v>
+        <v>0.0248</v>
       </c>
       <c r="G64" t="n">
-        <v>0.4101</v>
+        <v>0.4122</v>
       </c>
       <c r="H64" t="n">
-        <v>0.6539</v>
+        <v>0.6491</v>
       </c>
     </row>
     <row r="65">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.9048</v>
+        <v>0.9161</v>
       </c>
       <c r="F65" t="n">
-        <v>2.0301</v>
+        <v>0.0417</v>
       </c>
       <c r="G65" t="n">
-        <v>0.3665</v>
+        <v>0.3348</v>
       </c>
       <c r="H65" t="n">
-        <v>0.6572</v>
+        <v>0.6434</v>
       </c>
     </row>
     <row r="66">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9455</v>
+        <v>0.9418</v>
       </c>
       <c r="F66" t="n">
-        <v>2.0066</v>
+        <v>0.0511</v>
       </c>
       <c r="G66" t="n">
-        <v>0.3278</v>
+        <v>0.3294</v>
       </c>
       <c r="H66" t="n">
-        <v>0.6496</v>
+        <v>0.6403</v>
       </c>
     </row>
     <row r="67">
@@ -2554,20 +2554,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9065</v>
+        <v>0.9361</v>
       </c>
       <c r="F67" t="n">
-        <v>1.995</v>
+        <v>0.0863</v>
       </c>
       <c r="G67" t="n">
-        <v>0.3937</v>
+        <v>0.3158</v>
       </c>
       <c r="H67" t="n">
-        <v>0.6459</v>
+        <v>0.6283</v>
       </c>
     </row>
     <row r="68">
@@ -2586,20 +2586,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.944</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="F68" t="n">
-        <v>2.0025</v>
+        <v>0.0696</v>
       </c>
       <c r="G68" t="n">
-        <v>0.3265</v>
+        <v>0.2986</v>
       </c>
       <c r="H68" t="n">
-        <v>0.6483</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="69">
@@ -2618,20 +2618,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9435</v>
+        <v>0.9418</v>
       </c>
       <c r="F69" t="n">
-        <v>2.0559</v>
+        <v>-0.0167</v>
       </c>
       <c r="G69" t="n">
-        <v>0.341</v>
+        <v>0.3576</v>
       </c>
       <c r="H69" t="n">
-        <v>0.6653</v>
+        <v>0.6627999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9414</v>
+        <v>0.9326</v>
       </c>
       <c r="F70" t="n">
-        <v>2.0532</v>
+        <v>-0.0098</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3393</v>
+        <v>0.363</v>
       </c>
       <c r="H70" t="n">
-        <v>0.6645</v>
+        <v>0.6605</v>
       </c>
     </row>
     <row r="71">
@@ -2682,20 +2682,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9319</v>
+        <v>0.9432</v>
       </c>
       <c r="F71" t="n">
-        <v>2.0197</v>
+        <v>0.0051</v>
       </c>
       <c r="G71" t="n">
-        <v>0.3795</v>
+        <v>0.3573</v>
       </c>
       <c r="H71" t="n">
-        <v>0.6538</v>
+        <v>0.6556</v>
       </c>
     </row>
     <row r="72">
@@ -2714,20 +2714,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9292</v>
+        <v>0.9765</v>
       </c>
       <c r="F72" t="n">
-        <v>2.0508</v>
+        <v>-0.0189</v>
       </c>
       <c r="G72" t="n">
-        <v>0.3686</v>
+        <v>0.2412</v>
       </c>
       <c r="H72" t="n">
-        <v>0.6637</v>
+        <v>0.6635</v>
       </c>
     </row>
     <row r="73">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9436</v>
+        <v>0.9847</v>
       </c>
       <c r="F73" t="n">
-        <v>2.0231</v>
+        <v>-0.0146</v>
       </c>
       <c r="G73" t="n">
-        <v>0.385</v>
+        <v>0.2425</v>
       </c>
       <c r="H73" t="n">
-        <v>0.6549</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="74">
@@ -2778,20 +2778,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9257</v>
+        <v>0.9813</v>
       </c>
       <c r="F74" t="n">
-        <v>2.0623</v>
+        <v>-0.0568</v>
       </c>
       <c r="G74" t="n">
-        <v>0.4141</v>
+        <v>0.2683</v>
       </c>
       <c r="H74" t="n">
-        <v>0.6673</v>
+        <v>0.6757</v>
       </c>
     </row>
     <row r="75">
@@ -2810,20 +2810,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9183</v>
+        <v>0.8625</v>
       </c>
       <c r="F75" t="n">
-        <v>2.1139</v>
+        <v>-0.077</v>
       </c>
       <c r="G75" t="n">
-        <v>0.372</v>
+        <v>0.4357</v>
       </c>
       <c r="H75" t="n">
-        <v>0.6833</v>
+        <v>0.6821</v>
       </c>
     </row>
     <row r="76">
@@ -2842,20 +2842,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9183</v>
+        <v>0.8625</v>
       </c>
       <c r="F76" t="n">
-        <v>2.1139</v>
+        <v>-0.077</v>
       </c>
       <c r="G76" t="n">
-        <v>0.372</v>
+        <v>0.4357</v>
       </c>
       <c r="H76" t="n">
-        <v>0.6833</v>
+        <v>0.6821</v>
       </c>
     </row>
     <row r="77">
@@ -2874,20 +2874,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.8978</v>
       </c>
       <c r="F77" t="n">
-        <v>2.1095</v>
+        <v>-0.0392</v>
       </c>
       <c r="G77" t="n">
-        <v>0.3732</v>
+        <v>0.3735</v>
       </c>
       <c r="H77" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6701</v>
       </c>
     </row>
     <row r="78">
@@ -2906,20 +2906,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8993</v>
+        <v>0.8938</v>
       </c>
       <c r="F78" t="n">
-        <v>2.1084</v>
+        <v>-0.0409</v>
       </c>
       <c r="G78" t="n">
-        <v>0.3727</v>
+        <v>0.3768</v>
       </c>
       <c r="H78" t="n">
-        <v>0.6817</v>
+        <v>0.6706</v>
       </c>
     </row>
     <row r="79">
@@ -2938,20 +2938,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8994</v>
+        <v>0.893</v>
       </c>
       <c r="F79" t="n">
-        <v>2.1088</v>
+        <v>-0.0417</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3718</v>
+        <v>0.3758</v>
       </c>
       <c r="H79" t="n">
-        <v>0.6818</v>
+        <v>0.6709000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -2970,20 +2970,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8991</v>
+        <v>0.8935</v>
       </c>
       <c r="F80" t="n">
-        <v>2.108</v>
+        <v>-0.0402</v>
       </c>
       <c r="G80" t="n">
-        <v>0.3729</v>
+        <v>0.377</v>
       </c>
       <c r="H80" t="n">
-        <v>0.6815</v>
+        <v>0.6704</v>
       </c>
     </row>
     <row r="81">
@@ -3002,20 +3002,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.8689</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="F81" t="n">
-        <v>2.0371</v>
+        <v>0.0336</v>
       </c>
       <c r="G81" t="n">
-        <v>0.4105</v>
+        <v>0.3253</v>
       </c>
       <c r="H81" t="n">
-        <v>0.6594</v>
+        <v>0.6462</v>
       </c>
     </row>
     <row r="82">
@@ -3034,20 +3034,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.8648</v>
+        <v>0.9225</v>
       </c>
       <c r="F82" t="n">
-        <v>2.0399</v>
+        <v>0.0345</v>
       </c>
       <c r="G82" t="n">
-        <v>0.4119</v>
+        <v>0.3377</v>
       </c>
       <c r="H82" t="n">
-        <v>0.6603</v>
+        <v>0.6459</v>
       </c>
     </row>
     <row r="83">
@@ -3066,20 +3066,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9152</v>
+        <v>0.8659</v>
       </c>
       <c r="F83" t="n">
-        <v>2.1197</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>0.3729</v>
+        <v>0.4344</v>
       </c>
       <c r="H83" t="n">
-        <v>0.6851</v>
+        <v>0.6819</v>
       </c>
     </row>
     <row r="84">
@@ -3098,20 +3098,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.8658</v>
       </c>
       <c r="F84" t="n">
-        <v>2.1162</v>
+        <v>-0.0772</v>
       </c>
       <c r="G84" t="n">
-        <v>0.3561</v>
+        <v>0.4352</v>
       </c>
       <c r="H84" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6822</v>
       </c>
     </row>
     <row r="85">
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9324</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="F85" t="n">
-        <v>2.121</v>
+        <v>-0.0766</v>
       </c>
       <c r="G85" t="n">
-        <v>0.3535</v>
+        <v>0.4347</v>
       </c>
       <c r="H85" t="n">
-        <v>0.6855</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="86">
@@ -3162,20 +3162,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9762</v>
+        <v>0.9426</v>
       </c>
       <c r="F86" t="n">
-        <v>2.0353</v>
+        <v>0.0445</v>
       </c>
       <c r="G86" t="n">
-        <v>0.2931</v>
+        <v>0.369</v>
       </c>
       <c r="H86" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.6425</v>
       </c>
     </row>
     <row r="87">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9593</v>
+        <v>0.9679</v>
       </c>
       <c r="F87" t="n">
-        <v>2.0435</v>
+        <v>0.0462</v>
       </c>
       <c r="G87" t="n">
-        <v>0.3502</v>
+        <v>0.2669</v>
       </c>
       <c r="H87" t="n">
-        <v>0.6614</v>
+        <v>0.6419</v>
       </c>
     </row>
     <row r="88">
@@ -3226,20 +3226,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9555</v>
+        <v>0.9759</v>
       </c>
       <c r="F88" t="n">
-        <v>2.0236</v>
+        <v>0.0357</v>
       </c>
       <c r="G88" t="n">
-        <v>0.3349</v>
+        <v>0.2464</v>
       </c>
       <c r="H88" t="n">
-        <v>0.6551</v>
+        <v>0.6455</v>
       </c>
     </row>
     <row r="89">
@@ -3258,20 +3258,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9493</v>
+        <v>0.9623</v>
       </c>
       <c r="F89" t="n">
-        <v>2.0311</v>
+        <v>0.0202</v>
       </c>
       <c r="G89" t="n">
-        <v>0.3347</v>
+        <v>0.2968</v>
       </c>
       <c r="H89" t="n">
-        <v>0.6575</v>
+        <v>0.6506</v>
       </c>
     </row>
     <row r="90">
@@ -3290,20 +3290,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9492</v>
+        <v>0.9679</v>
       </c>
       <c r="F90" t="n">
-        <v>1.9932</v>
+        <v>0.0622</v>
       </c>
       <c r="G90" t="n">
-        <v>0.3693</v>
+        <v>0.3071</v>
       </c>
       <c r="H90" t="n">
-        <v>0.6453</v>
+        <v>0.6365</v>
       </c>
     </row>
     <row r="91">
@@ -3326,16 +3326,16 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9792</v>
+        <v>0.9823</v>
       </c>
       <c r="F91" t="n">
-        <v>1.9967</v>
+        <v>0.0333</v>
       </c>
       <c r="G91" t="n">
-        <v>0.2526</v>
+        <v>0.2372</v>
       </c>
       <c r="H91" t="n">
-        <v>0.6464</v>
+        <v>0.6463</v>
       </c>
     </row>
     <row r="92">
@@ -3354,20 +3354,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9555</v>
+        <v>0.9759</v>
       </c>
       <c r="F92" t="n">
-        <v>2.0236</v>
+        <v>0.0357</v>
       </c>
       <c r="G92" t="n">
-        <v>0.3349</v>
+        <v>0.2464</v>
       </c>
       <c r="H92" t="n">
-        <v>0.6551</v>
+        <v>0.6455</v>
       </c>
     </row>
     <row r="93">
@@ -3390,16 +3390,16 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9792</v>
+        <v>0.9823</v>
       </c>
       <c r="F93" t="n">
-        <v>1.9967</v>
+        <v>0.0333</v>
       </c>
       <c r="G93" t="n">
-        <v>0.2526</v>
+        <v>0.2372</v>
       </c>
       <c r="H93" t="n">
-        <v>0.6464</v>
+        <v>0.6463</v>
       </c>
     </row>
     <row r="94">
@@ -3418,20 +3418,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.9403</v>
       </c>
       <c r="F94" t="n">
-        <v>1.8785</v>
+        <v>0.241</v>
       </c>
       <c r="G94" t="n">
-        <v>0.3401</v>
+        <v>0.2647</v>
       </c>
       <c r="H94" t="n">
-        <v>0.6069</v>
+        <v>0.5726</v>
       </c>
     </row>
     <row r="95">
@@ -3454,16 +3454,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.7641</v>
+        <v>0.7716</v>
       </c>
       <c r="F95" t="n">
-        <v>2.0074</v>
+        <v>0.0142</v>
       </c>
       <c r="G95" t="n">
-        <v>0.4542</v>
+        <v>0.4503</v>
       </c>
       <c r="H95" t="n">
-        <v>0.6499</v>
+        <v>0.6526</v>
       </c>
     </row>
     <row r="96">
@@ -3482,20 +3482,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.8998</v>
+        <v>0.8941</v>
       </c>
       <c r="F96" t="n">
-        <v>1.8959</v>
+        <v>0.2377</v>
       </c>
       <c r="G96" t="n">
-        <v>0.3309</v>
+        <v>0.3288</v>
       </c>
       <c r="H96" t="n">
-        <v>0.6128</v>
+        <v>0.5739</v>
       </c>
     </row>
     <row r="97">
@@ -3514,20 +3514,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.8914</v>
+        <v>0.9021</v>
       </c>
       <c r="F97" t="n">
-        <v>1.8873</v>
+        <v>0.2387</v>
       </c>
       <c r="G97" t="n">
-        <v>0.3457</v>
+        <v>0.3165</v>
       </c>
       <c r="H97" t="n">
-        <v>0.6099</v>
+        <v>0.5735</v>
       </c>
     </row>
     <row r="98">
@@ -3546,20 +3546,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9341</v>
+        <v>0.9509</v>
       </c>
       <c r="F98" t="n">
-        <v>1.8507</v>
+        <v>0.2166</v>
       </c>
       <c r="G98" t="n">
-        <v>0.3053</v>
+        <v>0.2707</v>
       </c>
       <c r="H98" t="n">
-        <v>0.5972</v>
+        <v>0.5818</v>
       </c>
     </row>
     <row r="99">
@@ -3578,20 +3578,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9254</v>
+        <v>0.8964</v>
       </c>
       <c r="F99" t="n">
-        <v>1.8416</v>
+        <v>0.1844</v>
       </c>
       <c r="G99" t="n">
-        <v>0.3071</v>
+        <v>0.3417</v>
       </c>
       <c r="H99" t="n">
-        <v>0.594</v>
+        <v>0.5936</v>
       </c>
     </row>
     <row r="100">
@@ -3610,20 +3610,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9293</v>
+        <v>0.9397</v>
       </c>
       <c r="F100" t="n">
-        <v>1.8635</v>
+        <v>0.1831</v>
       </c>
       <c r="G100" t="n">
-        <v>0.2993</v>
+        <v>0.2764</v>
       </c>
       <c r="H100" t="n">
-        <v>0.6016</v>
+        <v>0.5941</v>
       </c>
     </row>
     <row r="101">
@@ -3642,20 +3642,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9154</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="F101" t="n">
-        <v>1.8741</v>
+        <v>0.1723</v>
       </c>
       <c r="G101" t="n">
-        <v>0.3207</v>
+        <v>0.3513</v>
       </c>
       <c r="H101" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="102">
@@ -3674,20 +3674,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9053</v>
+        <v>0.9664</v>
       </c>
       <c r="F102" t="n">
-        <v>1.8772</v>
+        <v>0.1788</v>
       </c>
       <c r="G102" t="n">
-        <v>0.3387</v>
+        <v>0.223</v>
       </c>
       <c r="H102" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.5956</v>
       </c>
     </row>
     <row r="103">
@@ -3706,20 +3706,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9201</v>
+        <v>0.9639</v>
       </c>
       <c r="F103" t="n">
-        <v>1.8619</v>
+        <v>0.1639</v>
       </c>
       <c r="G103" t="n">
-        <v>0.3392</v>
+        <v>0.2463</v>
       </c>
       <c r="H103" t="n">
-        <v>0.6011</v>
+        <v>0.601</v>
       </c>
     </row>
     <row r="104">
@@ -3738,20 +3738,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9443</v>
+        <v>0.9589</v>
       </c>
       <c r="F104" t="n">
-        <v>1.8381</v>
+        <v>0.1798</v>
       </c>
       <c r="G104" t="n">
-        <v>0.2863</v>
+        <v>0.2458</v>
       </c>
       <c r="H104" t="n">
-        <v>0.5928</v>
+        <v>0.5953000000000001</v>
       </c>
     </row>
     <row r="105">
@@ -3770,20 +3770,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="F105" t="n">
-        <v>1.8466</v>
+        <v>0.1703</v>
       </c>
       <c r="G105" t="n">
-        <v>0.2559</v>
+        <v>0.3399</v>
       </c>
       <c r="H105" t="n">
-        <v>0.5957</v>
+        <v>0.5987</v>
       </c>
     </row>
     <row r="106">
@@ -3802,20 +3802,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9333</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="F106" t="n">
-        <v>1.8315</v>
+        <v>0.1889</v>
       </c>
       <c r="G106" t="n">
-        <v>0.2965</v>
+        <v>0.315</v>
       </c>
       <c r="H106" t="n">
-        <v>0.5904</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="107">
@@ -3834,20 +3834,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9264</v>
+        <v>0.89</v>
       </c>
       <c r="F107" t="n">
-        <v>1.8762</v>
+        <v>0.1728</v>
       </c>
       <c r="G107" t="n">
-        <v>0.3052</v>
+        <v>0.3503</v>
       </c>
       <c r="H107" t="n">
-        <v>0.6061</v>
+        <v>0.5978</v>
       </c>
     </row>
     <row r="108">
@@ -3866,20 +3866,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9369</v>
+        <v>0.9439</v>
       </c>
       <c r="F108" t="n">
-        <v>1.8961</v>
+        <v>0.1641</v>
       </c>
       <c r="G108" t="n">
-        <v>0.3217</v>
+        <v>0.2959</v>
       </c>
       <c r="H108" t="n">
-        <v>0.6129</v>
+        <v>0.601</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9727</v>
+        <v>0.929</v>
       </c>
       <c r="F109" t="n">
-        <v>1.8934</v>
+        <v>0.1761</v>
       </c>
       <c r="G109" t="n">
-        <v>0.2378</v>
+        <v>0.3203</v>
       </c>
       <c r="H109" t="n">
-        <v>0.612</v>
+        <v>0.5966</v>
       </c>
     </row>
     <row r="110">
@@ -3930,20 +3930,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9548</v>
+        <v>0.9712</v>
       </c>
       <c r="F110" t="n">
-        <v>1.8498</v>
+        <v>0.1669</v>
       </c>
       <c r="G110" t="n">
-        <v>0.2592</v>
+        <v>0.2244</v>
       </c>
       <c r="H110" t="n">
-        <v>0.5969</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="111">
@@ -3962,20 +3962,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9282</v>
+        <v>0.9</v>
       </c>
       <c r="F111" t="n">
-        <v>1.8314</v>
+        <v>0.1571</v>
       </c>
       <c r="G111" t="n">
-        <v>0.3072</v>
+        <v>0.341</v>
       </c>
       <c r="H111" t="n">
-        <v>0.5904</v>
+        <v>0.6035</v>
       </c>
     </row>
     <row r="112">
@@ -3994,20 +3994,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.8921</v>
+        <v>0.9429</v>
       </c>
       <c r="F112" t="n">
-        <v>1.8981</v>
+        <v>0.1657</v>
       </c>
       <c r="G112" t="n">
-        <v>0.3779</v>
+        <v>0.2968</v>
       </c>
       <c r="H112" t="n">
-        <v>0.6136</v>
+        <v>0.6004</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9559</v>
+        <v>0.9301</v>
       </c>
       <c r="F113" t="n">
-        <v>1.8883</v>
+        <v>0.1759</v>
       </c>
       <c r="G113" t="n">
-        <v>0.2797</v>
+        <v>0.3192</v>
       </c>
       <c r="H113" t="n">
-        <v>0.6102</v>
+        <v>0.5967</v>
       </c>
     </row>
     <row r="114">
@@ -4058,20 +4058,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9267</v>
+        <v>0.9343</v>
       </c>
       <c r="F114" t="n">
-        <v>1.8536</v>
+        <v>0.1651</v>
       </c>
       <c r="G114" t="n">
-        <v>0.3107</v>
+        <v>0.3019</v>
       </c>
       <c r="H114" t="n">
-        <v>0.5982</v>
+        <v>0.6006</v>
       </c>
     </row>
     <row r="115">
@@ -4090,20 +4090,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.927</v>
+        <v>0.898</v>
       </c>
       <c r="F115" t="n">
-        <v>1.8302</v>
+        <v>0.1531</v>
       </c>
       <c r="G115" t="n">
-        <v>0.3073</v>
+        <v>0.3409</v>
       </c>
       <c r="H115" t="n">
-        <v>0.5899</v>
+        <v>0.6049</v>
       </c>
     </row>
     <row r="116">
@@ -4126,16 +4126,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9012</v>
+        <v>0.893</v>
       </c>
       <c r="F116" t="n">
-        <v>1.8922</v>
+        <v>0.0989</v>
       </c>
       <c r="G116" t="n">
-        <v>0.3443</v>
+        <v>0.3468</v>
       </c>
       <c r="H116" t="n">
-        <v>0.6116</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="117">
@@ -4158,16 +4158,16 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="F117" t="n">
-        <v>1.8925</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="G117" t="n">
-        <v>0.3982</v>
+        <v>0.4015</v>
       </c>
       <c r="H117" t="n">
-        <v>0.6117</v>
+        <v>0.6258</v>
       </c>
     </row>
     <row r="118">
@@ -4186,20 +4186,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="F118" t="n">
-        <v>1.8466</v>
+        <v>0.1703</v>
       </c>
       <c r="G118" t="n">
-        <v>0.2559</v>
+        <v>0.3399</v>
       </c>
       <c r="H118" t="n">
-        <v>0.5957</v>
+        <v>0.5987</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9559</v>
+        <v>0.9301</v>
       </c>
       <c r="F119" t="n">
-        <v>1.8883</v>
+        <v>0.1759</v>
       </c>
       <c r="G119" t="n">
-        <v>0.2797</v>
+        <v>0.3192</v>
       </c>
       <c r="H119" t="n">
-        <v>0.6102</v>
+        <v>0.5967</v>
       </c>
     </row>
     <row r="120">
@@ -4250,20 +4250,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.8717</v>
+        <v>0.8611</v>
       </c>
       <c r="F120" t="n">
-        <v>1.9518</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="G120" t="n">
-        <v>0.3661</v>
+        <v>0.3747</v>
       </c>
       <c r="H120" t="n">
-        <v>0.6317</v>
+        <v>0.6337</v>
       </c>
     </row>
     <row r="121">
@@ -4282,20 +4282,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.8717</v>
+        <v>0.8609</v>
       </c>
       <c r="F121" t="n">
-        <v>1.9518</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="G121" t="n">
-        <v>0.3661</v>
+        <v>0.3748</v>
       </c>
       <c r="H121" t="n">
-        <v>0.6317</v>
+        <v>0.6337</v>
       </c>
     </row>
     <row r="122">
@@ -4318,16 +4318,16 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9226</v>
+        <v>0.919</v>
       </c>
       <c r="F122" t="n">
-        <v>1.8631</v>
+        <v>0.1542</v>
       </c>
       <c r="G122" t="n">
-        <v>0.3141</v>
+        <v>0.3036</v>
       </c>
       <c r="H122" t="n">
-        <v>0.6015</v>
+        <v>0.6045</v>
       </c>
     </row>
     <row r="123">
@@ -4346,20 +4346,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9558</v>
+        <v>0.9301</v>
       </c>
       <c r="F123" t="n">
-        <v>1.8885</v>
+        <v>0.1756</v>
       </c>
       <c r="G123" t="n">
-        <v>0.2797</v>
+        <v>0.3193</v>
       </c>
       <c r="H123" t="n">
-        <v>0.6103</v>
+        <v>0.5968</v>
       </c>
     </row>
     <row r="124">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9115</v>
+        <v>0.9433</v>
       </c>
       <c r="F124" t="n">
-        <v>1.8598</v>
+        <v>0.1911</v>
       </c>
       <c r="G124" t="n">
-        <v>0.3414</v>
+        <v>0.2933</v>
       </c>
       <c r="H124" t="n">
-        <v>0.6004</v>
+        <v>0.5911999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -4410,20 +4410,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9661</v>
       </c>
       <c r="F125" t="n">
-        <v>1.8778</v>
+        <v>0.2445</v>
       </c>
       <c r="G125" t="n">
-        <v>0.3264</v>
+        <v>0.2158</v>
       </c>
       <c r="H125" t="n">
-        <v>0.6066</v>
+        <v>0.5713</v>
       </c>
     </row>
     <row r="126">
@@ -4442,20 +4442,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9536</v>
+        <v>0.8854</v>
       </c>
       <c r="F126" t="n">
-        <v>1.9328</v>
+        <v>0.0393</v>
       </c>
       <c r="G126" t="n">
-        <v>0.2837</v>
+        <v>0.3837</v>
       </c>
       <c r="H126" t="n">
-        <v>0.6254</v>
+        <v>0.6443</v>
       </c>
     </row>
     <row r="127">
@@ -4474,20 +4474,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.8697</v>
+        <v>0.8981</v>
       </c>
       <c r="F127" t="n">
-        <v>2.025</v>
+        <v>0.0241</v>
       </c>
       <c r="G127" t="n">
-        <v>0.394</v>
+        <v>0.3669</v>
       </c>
       <c r="H127" t="n">
-        <v>0.6555</v>
+        <v>0.6493</v>
       </c>
     </row>
     <row r="128">
@@ -4506,20 +4506,20 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.9115</v>
+        <v>0.9075</v>
       </c>
       <c r="F128" t="n">
-        <v>1.9495</v>
+        <v>0.044</v>
       </c>
       <c r="G128" t="n">
-        <v>0.3506</v>
+        <v>0.3573</v>
       </c>
       <c r="H128" t="n">
-        <v>0.6309</v>
+        <v>0.6427</v>
       </c>
     </row>
     <row r="129">
@@ -4538,20 +4538,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.9719</v>
+        <v>0.9608</v>
       </c>
       <c r="F129" t="n">
-        <v>1.9531</v>
+        <v>0.0429</v>
       </c>
       <c r="G129" t="n">
-        <v>0.2391</v>
+        <v>0.2667</v>
       </c>
       <c r="H129" t="n">
-        <v>0.6321</v>
+        <v>0.643</v>
       </c>
     </row>
     <row r="130">
@@ -4570,20 +4570,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.9717</v>
+        <v>0.8835</v>
       </c>
       <c r="F130" t="n">
-        <v>1.9424</v>
+        <v>0.043</v>
       </c>
       <c r="G130" t="n">
-        <v>0.2391</v>
+        <v>0.3822</v>
       </c>
       <c r="H130" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.643</v>
       </c>
     </row>
     <row r="131">
@@ -4602,20 +4602,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.9719</v>
+        <v>0.9268</v>
       </c>
       <c r="F131" t="n">
-        <v>1.9327</v>
+        <v>0.0408</v>
       </c>
       <c r="G131" t="n">
-        <v>0.2389</v>
+        <v>0.3253</v>
       </c>
       <c r="H131" t="n">
-        <v>0.6253</v>
+        <v>0.6438</v>
       </c>
     </row>
     <row r="132">
@@ -4634,20 +4634,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.973</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="F132" t="n">
-        <v>1.9575</v>
+        <v>0.0453</v>
       </c>
       <c r="G132" t="n">
-        <v>0.2408</v>
+        <v>0.2634</v>
       </c>
       <c r="H132" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6423</v>
       </c>
     </row>
     <row r="133">
@@ -4666,20 +4666,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.9216</v>
+        <v>0.9569</v>
       </c>
       <c r="F133" t="n">
-        <v>1.9483</v>
+        <v>0.0438</v>
       </c>
       <c r="G133" t="n">
-        <v>0.3325</v>
+        <v>0.2752</v>
       </c>
       <c r="H133" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.6428</v>
       </c>
     </row>
     <row r="134">
@@ -4698,20 +4698,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.9111</v>
+        <v>0.9084</v>
       </c>
       <c r="F134" t="n">
-        <v>1.9516</v>
+        <v>0.0443</v>
       </c>
       <c r="G134" t="n">
-        <v>0.3506</v>
+        <v>0.355</v>
       </c>
       <c r="H134" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6425999999999999</v>
       </c>
     </row>
     <row r="135">
@@ -4730,20 +4730,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.9185</v>
+        <v>0.962</v>
       </c>
       <c r="F135" t="n">
-        <v>1.9435</v>
+        <v>0.0465</v>
       </c>
       <c r="G135" t="n">
-        <v>0.3332</v>
+        <v>0.2636</v>
       </c>
       <c r="H135" t="n">
-        <v>0.6289</v>
+        <v>0.6418</v>
       </c>
     </row>
     <row r="136">
@@ -4766,16 +4766,16 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.9214</v>
+        <v>0.9266</v>
       </c>
       <c r="F136" t="n">
-        <v>1.9351</v>
+        <v>0.0497</v>
       </c>
       <c r="G136" t="n">
-        <v>0.3346</v>
+        <v>0.3231</v>
       </c>
       <c r="H136" t="n">
-        <v>0.6261</v>
+        <v>0.6407</v>
       </c>
     </row>
     <row r="137">
@@ -4794,20 +4794,20 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.975</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="F137" t="n">
-        <v>1.9708</v>
+        <v>0.0315</v>
       </c>
       <c r="G137" t="n">
-        <v>0.2426</v>
+        <v>0.3651</v>
       </c>
       <c r="H137" t="n">
-        <v>0.6379</v>
+        <v>0.6469</v>
       </c>
     </row>
     <row r="138">
@@ -4826,20 +4826,20 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9798</v>
+        <v>0.9744</v>
       </c>
       <c r="F138" t="n">
-        <v>1.9795</v>
+        <v>0.0324</v>
       </c>
       <c r="G138" t="n">
-        <v>0.2421</v>
+        <v>0.2406</v>
       </c>
       <c r="H138" t="n">
-        <v>0.6408</v>
+        <v>0.6466</v>
       </c>
     </row>
     <row r="139">
@@ -4862,16 +4862,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9658</v>
+        <v>0.9606</v>
       </c>
       <c r="F139" t="n">
-        <v>1.9551</v>
+        <v>0.0408</v>
       </c>
       <c r="G139" t="n">
-        <v>0.2738</v>
+        <v>0.2727</v>
       </c>
       <c r="H139" t="n">
-        <v>0.6328</v>
+        <v>0.6437</v>
       </c>
     </row>
     <row r="140">
@@ -4890,20 +4890,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.98</v>
+        <v>0.9653</v>
       </c>
       <c r="F140" t="n">
-        <v>2.0091</v>
+        <v>0.0516</v>
       </c>
       <c r="G140" t="n">
-        <v>0.283</v>
+        <v>0.3443</v>
       </c>
       <c r="H140" t="n">
-        <v>0.6504</v>
+        <v>0.6401</v>
       </c>
     </row>
     <row r="141">
@@ -4922,20 +4922,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9326</v>
+        <v>0.9732</v>
       </c>
       <c r="F141" t="n">
-        <v>2.0022</v>
+        <v>0.0594</v>
       </c>
       <c r="G141" t="n">
-        <v>0.3972</v>
+        <v>0.2623</v>
       </c>
       <c r="H141" t="n">
-        <v>0.6482</v>
+        <v>0.6375</v>
       </c>
     </row>
     <row r="142">
@@ -4954,20 +4954,20 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9798</v>
+        <v>0.9744</v>
       </c>
       <c r="F142" t="n">
-        <v>1.9795</v>
+        <v>0.0324</v>
       </c>
       <c r="G142" t="n">
-        <v>0.2421</v>
+        <v>0.2406</v>
       </c>
       <c r="H142" t="n">
-        <v>0.6408</v>
+        <v>0.6466</v>
       </c>
     </row>
     <row r="143">
@@ -4986,20 +4986,20 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.9465</v>
+        <v>0.9568</v>
       </c>
       <c r="F143" t="n">
-        <v>1.9985</v>
+        <v>0.0578</v>
       </c>
       <c r="G143" t="n">
-        <v>0.3112</v>
+        <v>0.29</v>
       </c>
       <c r="H143" t="n">
-        <v>0.647</v>
+        <v>0.638</v>
       </c>
     </row>
     <row r="144">
@@ -5018,20 +5018,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9442</v>
+        <v>0.8828</v>
       </c>
       <c r="F144" t="n">
-        <v>1.9674</v>
+        <v>0.0163</v>
       </c>
       <c r="G144" t="n">
-        <v>0.3097</v>
+        <v>0.4126</v>
       </c>
       <c r="H144" t="n">
-        <v>0.6368</v>
+        <v>0.6519</v>
       </c>
     </row>
     <row r="145">
@@ -5050,20 +5050,20 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.9326</v>
+        <v>0.9732</v>
       </c>
       <c r="F145" t="n">
-        <v>2.0022</v>
+        <v>0.0594</v>
       </c>
       <c r="G145" t="n">
-        <v>0.3972</v>
+        <v>0.2623</v>
       </c>
       <c r="H145" t="n">
-        <v>0.6482</v>
+        <v>0.6375</v>
       </c>
     </row>
     <row r="146">
@@ -5082,20 +5082,20 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.8701</v>
+        <v>0.8991</v>
       </c>
       <c r="F146" t="n">
-        <v>2.0198</v>
+        <v>0.0194</v>
       </c>
       <c r="G146" t="n">
-        <v>0.3943</v>
+        <v>0.365</v>
       </c>
       <c r="H146" t="n">
-        <v>0.6539</v>
+        <v>0.6509</v>
       </c>
     </row>
     <row r="147">
@@ -5114,20 +5114,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.8986</v>
       </c>
       <c r="F147" t="n">
-        <v>2.0187</v>
+        <v>0.0133</v>
       </c>
       <c r="G147" t="n">
-        <v>0.3963</v>
+        <v>0.3666</v>
       </c>
       <c r="H147" t="n">
-        <v>0.6535</v>
+        <v>0.6529</v>
       </c>
     </row>
     <row r="148">
@@ -5146,20 +5146,20 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.8659</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="F148" t="n">
-        <v>2.0183</v>
+        <v>0.0179</v>
       </c>
       <c r="G148" t="n">
-        <v>0.3974</v>
+        <v>0.3665</v>
       </c>
       <c r="H148" t="n">
-        <v>0.6534</v>
+        <v>0.6514</v>
       </c>
     </row>
     <row r="149">
@@ -5178,20 +5178,20 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.8677</v>
+        <v>0.8966</v>
       </c>
       <c r="F149" t="n">
-        <v>2.0106</v>
+        <v>0.0209</v>
       </c>
       <c r="G149" t="n">
-        <v>0.3942</v>
+        <v>0.3686</v>
       </c>
       <c r="H149" t="n">
-        <v>0.6509</v>
+        <v>0.6504</v>
       </c>
     </row>
     <row r="150">
@@ -5210,20 +5210,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.8691</v>
+        <v>0.8976</v>
       </c>
       <c r="F150" t="n">
-        <v>2.0286</v>
+        <v>0.0175</v>
       </c>
       <c r="G150" t="n">
-        <v>0.3939</v>
+        <v>0.3674</v>
       </c>
       <c r="H150" t="n">
-        <v>0.6567</v>
+        <v>0.6515</v>
       </c>
     </row>
     <row r="151">
@@ -5242,20 +5242,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.8685</v>
+        <v>0.8978</v>
       </c>
       <c r="F151" t="n">
-        <v>2.0272</v>
+        <v>0.0201</v>
       </c>
       <c r="G151" t="n">
-        <v>0.3944</v>
+        <v>0.3677</v>
       </c>
       <c r="H151" t="n">
-        <v>0.6562</v>
+        <v>0.6506999999999999</v>
       </c>
     </row>
     <row r="152">
@@ -5274,20 +5274,20 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.8692</v>
+        <v>0.8999</v>
       </c>
       <c r="F152" t="n">
-        <v>2.0244</v>
+        <v>0.0221</v>
       </c>
       <c r="G152" t="n">
-        <v>0.3944</v>
+        <v>0.366</v>
       </c>
       <c r="H152" t="n">
-        <v>0.6553</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="153">
@@ -5306,20 +5306,20 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.8688</v>
+        <v>0.9005</v>
       </c>
       <c r="F153" t="n">
-        <v>2.0214</v>
+        <v>0.0184</v>
       </c>
       <c r="G153" t="n">
-        <v>0.3942</v>
+        <v>0.365</v>
       </c>
       <c r="H153" t="n">
-        <v>0.6544</v>
+        <v>0.6512</v>
       </c>
     </row>
     <row r="154">
@@ -5338,20 +5338,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.8683999999999999</v>
+        <v>0.8992</v>
       </c>
       <c r="F154" t="n">
-        <v>2.0219</v>
+        <v>0.0138</v>
       </c>
       <c r="G154" t="n">
-        <v>0.3945</v>
+        <v>0.3665</v>
       </c>
       <c r="H154" t="n">
-        <v>0.6545</v>
+        <v>0.6526999999999999</v>
       </c>
     </row>
     <row r="155">
@@ -5370,20 +5370,20 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.8927</v>
+        <v>0.9408</v>
       </c>
       <c r="F155" t="n">
-        <v>2.03</v>
+        <v>0.0253</v>
       </c>
       <c r="G155" t="n">
-        <v>0.384</v>
+        <v>0.3157</v>
       </c>
       <c r="H155" t="n">
-        <v>0.6571</v>
+        <v>0.6489</v>
       </c>
     </row>
     <row r="156">
@@ -5402,20 +5402,20 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.896</v>
+        <v>0.918</v>
       </c>
       <c r="F156" t="n">
-        <v>2.0363</v>
+        <v>0.019</v>
       </c>
       <c r="G156" t="n">
-        <v>0.3781</v>
+        <v>0.345</v>
       </c>
       <c r="H156" t="n">
-        <v>0.6591</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="157">
@@ -5434,20 +5434,20 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.9527</v>
+        <v>0.9618</v>
       </c>
       <c r="F157" t="n">
-        <v>2.0325</v>
+        <v>0.0177</v>
       </c>
       <c r="G157" t="n">
-        <v>0.2993</v>
+        <v>0.2725</v>
       </c>
       <c r="H157" t="n">
-        <v>0.6579</v>
+        <v>0.6515</v>
       </c>
     </row>
     <row r="158">
@@ -5466,20 +5466,20 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.9245</v>
+        <v>0.8901</v>
       </c>
       <c r="F158" t="n">
-        <v>1.9721</v>
+        <v>0.0256</v>
       </c>
       <c r="G158" t="n">
-        <v>0.3585</v>
+        <v>0.4023</v>
       </c>
       <c r="H158" t="n">
-        <v>0.6384</v>
+        <v>0.6488</v>
       </c>
     </row>
     <row r="159">
@@ -5498,20 +5498,20 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.9721</v>
+        <v>0.9123</v>
       </c>
       <c r="F159" t="n">
-        <v>2.0018</v>
+        <v>0.013</v>
       </c>
       <c r="G159" t="n">
-        <v>0.2489</v>
+        <v>0.3662</v>
       </c>
       <c r="H159" t="n">
-        <v>0.6481</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="160">
@@ -5530,20 +5530,20 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.9039</v>
+        <v>0.9031</v>
       </c>
       <c r="F160" t="n">
-        <v>2.008</v>
+        <v>0.0411</v>
       </c>
       <c r="G160" t="n">
-        <v>0.3621</v>
+        <v>0.3604</v>
       </c>
       <c r="H160" t="n">
-        <v>0.6501</v>
+        <v>0.6437</v>
       </c>
     </row>
     <row r="161">
@@ -5562,20 +5562,20 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.9014</v>
+        <v>0.9169</v>
       </c>
       <c r="F161" t="n">
-        <v>1.9991</v>
+        <v>0.0426</v>
       </c>
       <c r="G161" t="n">
-        <v>0.3629</v>
+        <v>0.3447</v>
       </c>
       <c r="H161" t="n">
-        <v>0.6472</v>
+        <v>0.6431</v>
       </c>
     </row>
     <row r="162">
@@ -5594,20 +5594,20 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.896</v>
+        <v>0.9724</v>
       </c>
       <c r="F162" t="n">
-        <v>2.0163</v>
+        <v>0.0104</v>
       </c>
       <c r="G162" t="n">
-        <v>0.3822</v>
+        <v>0.2364</v>
       </c>
       <c r="H162" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.6539</v>
       </c>
     </row>
     <row r="163">
@@ -5626,20 +5626,20 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.8914</v>
+        <v>0.928</v>
       </c>
       <c r="F163" t="n">
-        <v>2.0228</v>
+        <v>0.0505</v>
       </c>
       <c r="G163" t="n">
-        <v>0.4072</v>
+        <v>0.361</v>
       </c>
       <c r="H163" t="n">
-        <v>0.6548</v>
+        <v>0.6405</v>
       </c>
     </row>
     <row r="164">
@@ -5658,20 +5658,20 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.9802</v>
+        <v>0.9654</v>
       </c>
       <c r="F164" t="n">
-        <v>2.0084</v>
+        <v>0.0518</v>
       </c>
       <c r="G164" t="n">
-        <v>0.2827</v>
+        <v>0.3441</v>
       </c>
       <c r="H164" t="n">
-        <v>0.6502</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="165">
@@ -5690,20 +5690,20 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9661</v>
       </c>
       <c r="F165" t="n">
-        <v>1.8778</v>
+        <v>0.2445</v>
       </c>
       <c r="G165" t="n">
-        <v>0.3264</v>
+        <v>0.2158</v>
       </c>
       <c r="H165" t="n">
-        <v>0.6066</v>
+        <v>0.5713</v>
       </c>
     </row>
     <row r="166">
@@ -5726,16 +5726,16 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.7749</v>
       </c>
       <c r="F166" t="n">
-        <v>2.0114</v>
+        <v>0.0164</v>
       </c>
       <c r="G166" t="n">
-        <v>0.4548</v>
+        <v>0.4482</v>
       </c>
       <c r="H166" t="n">
-        <v>0.6511</v>
+        <v>0.6519</v>
       </c>
     </row>
     <row r="167">
@@ -5754,20 +5754,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.9574</v>
+        <v>0.964</v>
       </c>
       <c r="F167" t="n">
-        <v>1.9553</v>
+        <v>0.0808</v>
       </c>
       <c r="G167" t="n">
-        <v>0.3041</v>
+        <v>0.2838</v>
       </c>
       <c r="H167" t="n">
-        <v>0.6328</v>
+        <v>0.6302</v>
       </c>
     </row>
     <row r="168">
@@ -5786,20 +5786,20 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9503</v>
+        <v>0.9599</v>
       </c>
       <c r="F168" t="n">
-        <v>1.9897</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G168" t="n">
-        <v>0.3596</v>
+        <v>0.3508</v>
       </c>
       <c r="H168" t="n">
-        <v>0.6441</v>
+        <v>0.6277</v>
       </c>
     </row>
     <row r="169">
@@ -5818,20 +5818,20 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9671</v>
+        <v>0.9787</v>
       </c>
       <c r="F169" t="n">
-        <v>1.9658</v>
+        <v>0.0727</v>
       </c>
       <c r="G169" t="n">
-        <v>0.2836</v>
+        <v>0.2339</v>
       </c>
       <c r="H169" t="n">
-        <v>0.6363</v>
+        <v>0.6329</v>
       </c>
     </row>
     <row r="170">
@@ -5850,20 +5850,20 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.9473</v>
+        <v>0.9775</v>
       </c>
       <c r="F170" t="n">
-        <v>2.0229</v>
+        <v>-0.0187</v>
       </c>
       <c r="G170" t="n">
-        <v>0.3799</v>
+        <v>0.2716</v>
       </c>
       <c r="H170" t="n">
-        <v>0.6548</v>
+        <v>0.6634</v>
       </c>
     </row>
     <row r="171">
@@ -5882,20 +5882,20 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9393</v>
+        <v>0.9852</v>
       </c>
       <c r="F171" t="n">
-        <v>1.9997</v>
+        <v>0.0573</v>
       </c>
       <c r="G171" t="n">
-        <v>0.3869</v>
+        <v>0.2573</v>
       </c>
       <c r="H171" t="n">
-        <v>0.6474</v>
+        <v>0.6382</v>
       </c>
     </row>
     <row r="172">
@@ -5914,20 +5914,20 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9771</v>
+        <v>0.9257</v>
       </c>
       <c r="F172" t="n">
-        <v>2.0243</v>
+        <v>0.0229</v>
       </c>
       <c r="G172" t="n">
-        <v>0.2415</v>
+        <v>0.3375</v>
       </c>
       <c r="H172" t="n">
-        <v>0.6553</v>
+        <v>0.6497000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C18.1n7/RANDOMSEARCH_DETAILS_C18.1n7.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C18.1n7/RANDOMSEARCH_DETAILS_C18.1n7.xlsx
@@ -4698,17 +4698,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.9082</v>
+        <v>0.9084</v>
       </c>
       <c r="F134" t="n">
         <v>0.0443</v>
       </c>
       <c r="G134" t="n">
-        <v>0.3551</v>
+        <v>0.355</v>
       </c>
       <c r="H134" t="n">
         <v>0.6425999999999999</v>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E146" t="n">
